--- a/c/拖课统计.xlsx
+++ b/c/拖课统计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="20750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="拖课统计" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="39">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -55,6 +55,9 @@
     <t>体育</t>
   </si>
   <si>
+    <t>信息</t>
+  </si>
+  <si>
     <t>历史</t>
   </si>
   <si>
@@ -70,10 +73,10 @@
     <t>劳技</t>
   </si>
   <si>
-    <t>跑操/圈</t>
+    <t>地理</t>
   </si>
   <si>
-    <t>地理</t>
+    <t>跑操/圈</t>
   </si>
   <si>
     <t>音乐</t>
@@ -2723,24 +2726,28 @@
       <c r="C3" s="16">
         <v>1</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="16">
+      <c r="I3" s="16">
         <v>1.25</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="J3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="16">
+      <c r="K3" s="16">
         <v>1.25</v>
       </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="16"/>
+      <c r="L3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="16">
+        <v>1.5</v>
+      </c>
       <c r="N3" s="15"/>
       <c r="O3" s="16"/>
       <c r="P3" s="15"/>
@@ -3383,24 +3390,28 @@
       <c r="C5" s="22">
         <v>3</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="22">
+      <c r="I5" s="22">
         <v>5.25</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="J5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="K5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="22"/>
+      <c r="L5" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="22" t="s">
+        <v>4</v>
+      </c>
       <c r="N5" s="21"/>
       <c r="O5" s="22"/>
       <c r="P5" s="21"/>
@@ -4043,24 +4054,28 @@
       <c r="C7" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="23"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="I7" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="J7" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="22">
+      <c r="K7" s="22">
         <v>3.25</v>
       </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="22"/>
+      <c r="L7" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" s="22" t="s">
+        <v>4</v>
+      </c>
       <c r="N7" s="23"/>
       <c r="O7" s="22"/>
       <c r="P7" s="23"/>
@@ -4374,16 +4389,16 @@
       <c r="A8" s="17"/>
       <c r="B8" s="18"/>
       <c r="C8" s="19"/>
-      <c r="D8" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="19">
-        <v>1</v>
-      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="19"/>
       <c r="F8" s="18"/>
       <c r="G8" s="19"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="19"/>
+      <c r="H8" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="19">
+        <v>1</v>
+      </c>
       <c r="J8" s="18"/>
       <c r="K8" s="19"/>
       <c r="L8" s="18"/>
@@ -4702,29 +4717,33 @@
         <v>4</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="22">
+      <c r="I9" s="22">
         <v>1.75</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="J9" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="K9" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="21"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="22"/>
+      <c r="L9" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="M9" s="22">
+        <v>3</v>
+      </c>
       <c r="N9" s="21"/>
       <c r="O9" s="22"/>
       <c r="P9" s="21"/>
@@ -5359,28 +5378,32 @@
     </row>
     <row r="11" s="7" customFormat="1" ht="25" customHeight="1" spans="1:321">
       <c r="A11" s="20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
-      <c r="D11" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="22" t="s">
+      <c r="D11" s="21"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="J11" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="K11" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="22"/>
+      <c r="L11" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="M11" s="22" t="s">
+        <v>4</v>
+      </c>
       <c r="N11" s="21"/>
       <c r="O11" s="22"/>
       <c r="P11" s="21"/>
@@ -6019,24 +6042,28 @@
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="22" t="s">
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="22" t="s">
+      <c r="J13" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="K13" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="22"/>
+      <c r="L13" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="22" t="s">
+        <v>4</v>
+      </c>
       <c r="N13" s="21"/>
       <c r="O13" s="22"/>
       <c r="P13" s="21"/>
@@ -6675,24 +6702,28 @@
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="I15" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="22" t="s">
+      <c r="J15" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="22"/>
+      <c r="L15" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" s="22">
+        <v>2</v>
+      </c>
       <c r="N15" s="21"/>
       <c r="O15" s="22"/>
       <c r="P15" s="21"/>
@@ -7331,24 +7362,28 @@
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
-      <c r="D17" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="22" t="s">
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="J17" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="K17" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="22"/>
+      <c r="L17" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="M17" s="22">
+        <v>1.75</v>
+      </c>
       <c r="N17" s="21"/>
       <c r="O17" s="22"/>
       <c r="P17" s="21"/>
@@ -7987,24 +8022,28 @@
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="21"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E19" s="22">
+      <c r="I19" s="22">
         <v>0.5</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="J19" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="G19" s="22">
+      <c r="K19" s="22">
         <v>2.5</v>
       </c>
-      <c r="H19" s="21"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="22"/>
+      <c r="L19" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="M19" s="22" t="s">
+        <v>4</v>
+      </c>
       <c r="N19" s="21"/>
       <c r="O19" s="22"/>
       <c r="P19" s="21"/>
@@ -8640,643 +8679,643 @@
     <row r="21" ht="17.5" spans="1:321">
       <c r="A21" s="27"/>
       <c r="B21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E21" s="29"/>
       <c r="F21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G21" s="29"/>
       <c r="H21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I21" s="29"/>
       <c r="J21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K21" s="29"/>
       <c r="L21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M21" s="29"/>
       <c r="N21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O21" s="29"/>
       <c r="P21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q21" s="29"/>
       <c r="R21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S21" s="29"/>
       <c r="T21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U21" s="29"/>
       <c r="V21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W21" s="29"/>
       <c r="X21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y21" s="29"/>
       <c r="Z21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA21" s="29"/>
       <c r="AB21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AC21" s="29"/>
       <c r="AD21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE21" s="29"/>
       <c r="AF21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG21" s="29"/>
       <c r="AH21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI21" s="29"/>
       <c r="AJ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK21" s="29"/>
       <c r="AL21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM21" s="29"/>
       <c r="AN21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO21" s="29"/>
       <c r="AP21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ21" s="29"/>
       <c r="AR21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS21" s="29"/>
       <c r="AT21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU21" s="29"/>
       <c r="AV21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW21" s="29"/>
       <c r="AX21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY21" s="29"/>
       <c r="AZ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA21" s="29"/>
       <c r="BB21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC21" s="29"/>
       <c r="BD21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BE21" s="29"/>
       <c r="BF21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BG21" s="29"/>
       <c r="BH21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BI21" s="29"/>
       <c r="BJ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BK21" s="29"/>
       <c r="BL21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BM21" s="29"/>
       <c r="BN21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BO21" s="29"/>
       <c r="BP21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BQ21" s="29"/>
       <c r="BR21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BS21" s="29"/>
       <c r="BT21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BU21" s="29"/>
       <c r="BV21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW21" s="29"/>
       <c r="BX21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BY21" s="29"/>
       <c r="BZ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CA21" s="29"/>
       <c r="CB21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CC21" s="29"/>
       <c r="CD21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CE21" s="29"/>
       <c r="CF21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CG21" s="29"/>
       <c r="CH21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CI21" s="29"/>
       <c r="CJ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CK21" s="29"/>
       <c r="CL21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CM21" s="29"/>
       <c r="CN21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CO21" s="29"/>
       <c r="CP21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CQ21" s="29"/>
       <c r="CR21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CS21" s="29"/>
       <c r="CT21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CU21" s="29"/>
       <c r="CV21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW21" s="29"/>
       <c r="CX21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CY21" s="29"/>
       <c r="CZ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DA21" s="29"/>
       <c r="DB21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DC21" s="29"/>
       <c r="DD21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DE21" s="29"/>
       <c r="DF21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DG21" s="29"/>
       <c r="DH21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DI21" s="29"/>
       <c r="DJ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DK21" s="29"/>
       <c r="DL21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DM21" s="29"/>
       <c r="DN21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DO21" s="29"/>
       <c r="DP21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DQ21" s="29"/>
       <c r="DR21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DS21" s="29"/>
       <c r="DT21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DU21" s="29"/>
       <c r="DV21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DW21" s="29"/>
       <c r="DX21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DY21" s="29"/>
       <c r="DZ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EA21" s="29"/>
       <c r="EB21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EC21" s="29"/>
       <c r="ED21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EE21" s="29"/>
       <c r="EF21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EG21" s="29"/>
       <c r="EH21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EI21" s="29"/>
       <c r="EJ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EK21" s="29"/>
       <c r="EL21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EM21" s="29"/>
       <c r="EN21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EO21" s="29"/>
       <c r="EP21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EQ21" s="29"/>
       <c r="ER21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="ES21" s="29"/>
       <c r="ET21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EU21" s="29"/>
       <c r="EV21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EW21" s="29"/>
       <c r="EX21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EY21" s="29"/>
       <c r="EZ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FA21" s="29"/>
       <c r="FB21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FC21" s="29"/>
       <c r="FD21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FE21" s="29"/>
       <c r="FF21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FG21" s="29"/>
       <c r="FH21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FI21" s="29"/>
       <c r="FJ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FK21" s="29"/>
       <c r="FL21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FM21" s="29"/>
       <c r="FN21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FO21" s="29"/>
       <c r="FP21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FQ21" s="29"/>
       <c r="FR21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FS21" s="29"/>
       <c r="FT21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FU21" s="29"/>
       <c r="FV21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FW21" s="29"/>
       <c r="FX21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="FY21" s="29"/>
       <c r="FZ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GA21" s="29"/>
       <c r="GB21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GC21" s="29"/>
       <c r="GD21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GE21" s="29"/>
       <c r="GF21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GG21" s="29"/>
       <c r="GH21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GI21" s="29"/>
       <c r="GJ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GK21" s="29"/>
       <c r="GL21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GM21" s="29"/>
       <c r="GN21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GO21" s="29"/>
       <c r="GP21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GQ21" s="29"/>
       <c r="GR21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GS21" s="29"/>
       <c r="GT21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GU21" s="29"/>
       <c r="GV21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GW21" s="29"/>
       <c r="GX21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="GY21" s="29"/>
       <c r="GZ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HA21" s="29"/>
       <c r="HB21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HC21" s="29"/>
       <c r="HD21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HE21" s="29"/>
       <c r="HF21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HG21" s="29"/>
       <c r="HH21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HI21" s="29"/>
       <c r="HJ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HK21" s="29"/>
       <c r="HL21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HM21" s="29"/>
       <c r="HN21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HO21" s="29"/>
       <c r="HP21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HQ21" s="29"/>
       <c r="HR21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HS21" s="29"/>
       <c r="HT21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HU21" s="29"/>
       <c r="HV21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HW21" s="29"/>
       <c r="HX21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="HY21" s="29"/>
       <c r="HZ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IA21" s="29"/>
       <c r="IB21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IC21" s="29"/>
       <c r="ID21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IE21" s="29"/>
       <c r="IF21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IG21" s="29"/>
       <c r="IH21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="II21" s="29"/>
       <c r="IJ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IK21" s="29"/>
       <c r="IL21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IM21" s="29"/>
       <c r="IN21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IO21" s="29"/>
       <c r="IP21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IQ21" s="29"/>
       <c r="IR21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IS21" s="29"/>
       <c r="IT21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IU21" s="29"/>
       <c r="IV21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IW21" s="29"/>
       <c r="IX21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="IY21" s="29"/>
       <c r="IZ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JA21" s="29"/>
       <c r="JB21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JC21" s="29"/>
       <c r="JD21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JE21" s="29"/>
       <c r="JF21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JG21" s="29"/>
       <c r="JH21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JI21" s="29"/>
       <c r="JJ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JK21" s="29"/>
       <c r="JL21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JM21" s="29"/>
       <c r="JN21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JO21" s="29"/>
       <c r="JP21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JQ21" s="29"/>
       <c r="JR21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JS21" s="29"/>
       <c r="JT21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JU21" s="29"/>
       <c r="JV21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JW21" s="29"/>
       <c r="JX21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="JY21" s="29"/>
       <c r="JZ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KA21" s="29"/>
       <c r="KB21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KC21" s="29"/>
       <c r="KD21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KE21" s="29"/>
       <c r="KF21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KG21" s="29"/>
       <c r="KH21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KI21" s="29"/>
       <c r="KJ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KK21" s="29"/>
       <c r="KL21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KM21" s="29"/>
       <c r="KN21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KO21" s="29"/>
       <c r="KP21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KQ21" s="29"/>
       <c r="KR21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KS21" s="29"/>
       <c r="KT21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KU21" s="29"/>
       <c r="KV21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KW21" s="29"/>
       <c r="KX21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="KY21" s="29"/>
       <c r="KZ21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="LA21" s="29"/>
       <c r="LB21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="LC21" s="29"/>
       <c r="LD21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="LE21" s="29"/>
       <c r="LF21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="LG21" s="29"/>
       <c r="LH21" s="28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="LI21" s="29"/>
     </row>
@@ -9447,26 +9486,26 @@
     <mergeCell ref="LF2:LG2"/>
     <mergeCell ref="LH2:LI2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:B20 D3:D20 F3:F20 H3:H20 J3:J20 L3:L20 N3:N20 P3:P20 R3:R20 T3:T20 V3:V20 X3:X20 Z3:Z20 AB3:AB20 AD3:AD20 AF3:AF20 AH3:AH20 AJ3:AJ20 AL3:AL20 AN3:AN20 AP3:AP20 AR3:AR20 AT3:AT20 AV3:AV20 AX3:AX20 AZ3:AZ20 BB3:BB20 BD3:BD20 BF3:BF20 BH3:BH20 BJ3:BJ20 BL3:BL20 BN3:BN20 BP3:BP20 BR3:BR20 BT3:BT20 BV3:BV20 BX3:BX20 BZ3:BZ20 CB3:CB20 CD3:CD20 CF3:CF20 CH3:CH20 CJ3:CJ20 CL3:CL20 CN3:CN20 CP3:CP20 CR3:CR20 CT3:CT20 CV3:CV20 CX3:CX20 CZ3:CZ20 DB3:DB20 DD3:DD20 DF3:DF20 DH3:DH20 DJ3:DJ20 DL3:DL20 DN3:DN20 DP3:DP20 DR3:DR20 DT3:DT20 DV3:DV20 DX3:DX20 DZ3:DZ20 EB3:EB20 ED3:ED20 EF3:EF20 EH3:EH20 EJ3:EJ20 EL3:EL20 EN3:EN20 EP3:EP20 ER3:ER20 ET3:ET20 EV3:EV20 EX3:EX20 EZ3:EZ20 FB3:FB20 FD3:FD20 FF3:FF20 FH3:FH20 FJ3:FJ20 FL3:FL20 FN3:FN20 FP3:FP20 FR3:FR20 FT3:FT20 FV3:FV20 FX3:FX20 FZ3:FZ20 GB3:GB20 GD3:GD20 GF3:GF20 GH3:GH20 GJ3:GJ20 GL3:GL20 GN3:GN20 GP3:GP20 GR3:GR20 GT3:GT20 GV3:GV20 GX3:GX20 GZ3:GZ20 HB3:HB20 HD3:HD20 HF3:HF20 HH3:HH20 HJ3:HJ20 HL3:HL20 HN3:HN20 HP3:HP20 HR3:HR20 HT3:HT20 HV3:HV20 HX3:HX20 HZ3:HZ20 IB3:IB20 ID3:ID20 IF3:IF20 IH3:IH20 IJ3:IJ20 IL3:IL20 IN3:IN20 IP3:IP20 IR3:IR20 IT3:IT20 IV3:IV20 IX3:IX20 IZ3:IZ20 JB3:JB20 JD3:JD20 JF3:JF20 JH3:JH20 JJ3:JJ20 JL3:JL20 JN3:JN20 JP3:JP20 JR3:JR20 JT3:JT20 JV3:JV20 JX3:JX20 JZ3:JZ20 KB3:KB20 KD3:KD20 KF3:KF20 KH3:KH20 KJ3:KJ20 KL3:KL20 KN3:KN20 KP3:KP20 KR3:KR20 KT3:KT20 KV3:KV20 KX3:KX20 KZ3:KZ20 LB3:LB20 LD3:LD20 LF3:LF20 LH3:LH20">
+  <conditionalFormatting sqref="B3:B20 D3:D20 LH3:LH20 F3:F20 LF3:LF20 H3:H20 LD3:LD20 J3:J20 LB3:LB20 L3:L20 KZ3:KZ20 N3:N20 P3:P20 R3:R20 T3:T20 V3:V20 X3:X20 Z3:Z20 AB3:AB20 AD3:AD20 AF3:AF20 AH3:AH20 AJ3:AJ20 AL3:AL20 AN3:AN20 AP3:AP20 AR3:AR20 AT3:AT20 AV3:AV20 AX3:AX20 AZ3:AZ20 BB3:BB20 BD3:BD20 BF3:BF20 BH3:BH20 BJ3:BJ20 BL3:BL20 BN3:BN20 BP3:BP20 BR3:BR20 BT3:BT20 BV3:BV20 BX3:BX20 BZ3:BZ20 CB3:CB20 CD3:CD20 CF3:CF20 CH3:CH20 CJ3:CJ20 CL3:CL20 CN3:CN20 CP3:CP20 CR3:CR20 CT3:CT20 CV3:CV20 CX3:CX20 CZ3:CZ20 DB3:DB20 DD3:DD20 DF3:DF20 DH3:DH20 DJ3:DJ20 DL3:DL20 DN3:DN20 DP3:DP20 DR3:DR20 DT3:DT20 DV3:DV20 DX3:DX20 DZ3:DZ20 EB3:EB20 ED3:ED20 EF3:EF20 EH3:EH20 EJ3:EJ20 EL3:EL20 EN3:EN20 EP3:EP20 ER3:ER20 ET3:ET20 EV3:EV20 EX3:EX20 EZ3:EZ20 FB3:FB20 FD3:FD20 FF3:FF20 FH3:FH20 FJ3:FJ20 FL3:FL20 FN3:FN20 FP3:FP20 FR3:FR20 FT3:FT20 FV3:FV20 FX3:FX20 FZ3:FZ20 GB3:GB20 GD3:GD20 GF3:GF20 GH3:GH20 GJ3:GJ20 GL3:GL20 GN3:GN20 GP3:GP20 GR3:GR20 GT3:GT20 GV3:GV20 GX3:GX20 GZ3:GZ20 HB3:HB20 HD3:HD20 HF3:HF20 HH3:HH20 HJ3:HJ20 HL3:HL20 HN3:HN20 HP3:HP20 HR3:HR20 HT3:HT20 HV3:HV20 HX3:HX20 HZ3:HZ20 IB3:IB20 ID3:ID20 IF3:IF20 IH3:IH20 IJ3:IJ20 IL3:IL20 IN3:IN20 IP3:IP20 IR3:IR20 IT3:IT20 IV3:IV20 IX3:IX20 IZ3:IZ20 JB3:JB20 JD3:JD20 JF3:JF20 JH3:JH20 JJ3:JJ20 JL3:JL20 JN3:JN20 JP3:JP20 JR3:JR20 JT3:JT20 JV3:JV20 JX3:JX20 JZ3:JZ20 KB3:KB20 KD3:KD20 KF3:KF20 KH3:KH20 KJ3:KJ20 KL3:KL20 KN3:KN20 KP3:KP20 KR3:KR20 KT3:KT20 KV3:KV20 KX3:KX20">
     <cfRule type="containsText" dxfId="0" priority="3" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3 C5 C7 C9 C11 C13 C15 C17 C19 E3 E5 E11 E13 E15 E17 E19 E7 E9 G3 I3 K3 M3 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DC3 DE3 DG3 DI3 DK3 DM3 DO3 DQ3 DS3 DU3 DW3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 G5 I5 K5 M5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DC5 DE5 DG5 DI5 DK5 DM5 DO5 DQ5 DS5 DU5 DW5 DY5 EA5 EC5 EE5 EG5 EI5 EK5 EM5 EO5 EQ5 ES5 EU5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 KI5 KK5 KM5 KO5 KQ5 KS5 KU5 KW5 KY5 LA5 LC5 LE5 LG5 LI5 G7 I7 K7 M7 O7 Q7 S7 U7 W7 Y7 AA7 AC7 AE7 AG7 AI7 AK7 AM7 AO7 AQ7 AS7 AU7 AW7 AY7 BA7 BC7 BE7 BG7 BI7 BK7 BM7 BO7 BQ7 BS7 BU7 BW7 BY7 CA7 CC7 CE7 CG7 CI7 CK7 CM7 CO7 CQ7 CS7 CU7 CW7 CY7 DA7 DC7 DE7 DG7 DI7 DK7 DM7 DO7 DQ7 DS7 DU7 DW7 DY7 EA7 EC7 EE7 EG7 EI7 EK7 EM7 EO7 EQ7 ES7 EU7 EW7 EY7 FA7 FC7 FE7 FG7 FI7 FK7 FM7 FO7 FQ7 FS7 FU7 FW7 FY7 GA7 GC7 GE7 GG7 GI7 GK7 GM7 GO7 GQ7 GS7 GU7 GW7 GY7 HA7 HC7 HE7 HG7 HI7 HK7 HM7 HO7 HQ7 HS7 HU7 HW7 HY7 IA7 IC7 IE7 IG7 II7 IK7 IM7 IO7 IQ7 IS7 IU7 IW7 IY7 JA7 JC7 JE7 JG7 JI7 JK7 JM7 JO7 JQ7 JS7 JU7 JW7 JY7 KA7 KC7 KE7 KG7 KI7 KK7 KM7 KO7 KQ7 KS7 KU7 KW7 KY7 LA7 LC7 LE7 LG7 LI7 G9 I9 K9 M9 O9 Q9 S9 U9 W9 Y9 AA9 AC9 AE9 AG9 AI9 AK9 AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BW9 BY9 CA9 CC9 CE9 CG9 CI9 CK9 CM9 CO9 CQ9 CS9 CU9 CW9 CY9 DA9 DC9 DE9 DG9 DI9 DK9 DM9 DO9 DQ9 DS9 DU9 DW9 DY9 EA9 EC9 EE9 EG9 EI9 EK9 EM9 EO9 EQ9 ES9 EU9 EW9 EY9 FA9 FC9 FE9 FG9 FI9 FK9 FM9 FO9 FQ9 FS9 FU9 FW9 FY9 GA9 GC9 GE9 GG9 GI9 GK9 GM9 GO9 GQ9 GS9 GU9 GW9 GY9 HA9 HC9 HE9 HG9 HI9 HK9 HM9 HO9 HQ9 HS9 HU9 HW9 HY9 IA9 IC9 IE9 IG9 II9 IK9 IM9 IO9 IQ9 IS9 IU9 IW9 IY9 JA9 JC9 JE9 JG9 JI9 JK9 JM9 JO9 JQ9 JS9 JU9 JW9 JY9 KA9 KC9 KE9 KG9 KI9 KK9 KM9 KO9 KQ9 KS9 KU9 KW9 KY9 LA9 LC9 LE9 LG9 LI9 G11 I11 K11 M11 O11 Q11 S11 U11 W11 Y11 AA11 AC11 AE11 AG11 AI11 AK11 AM11 AO11 AQ11 AS11 AU11 AW11 AY11 BA11 BC11 BE11 BG11 BI11 BK11 BM11 BO11 BQ11 BS11 BU11 BW11 BY11 CA11 CC11 CE11 CG11 CI11 CK11 CM11 CO11 CQ11 CS11 CU11 CW11 CY11 DA11 DC11 DE11 DG11 DI11 DK11 DM11 DO11 DQ11 DS11 DU11 DW11 DY11 EA11 EC11 EE11 EG11 EI11 EK11 EM11 EO11 EQ11 ES11 EU11 EW11 EY11 FA11 FC11 FE11 FG11 FI11 FK11 FM11 FO11 FQ11 FS11 FU11 FW11 FY11 GA11 GC11 GE11 GG11 GI11 GK11 GM11 GO11 GQ11 GS11 GU11 GW11 GY11 HA11 HC11 HE11 HG11 HI11 HK11 HM11 HO11 HQ11 HS11 HU11 HW11 HY11 IA11 IC11 IE11 IG11 II11 IK11 IM11 IO11 IQ11 IS11 IU11 IW11 IY11 JA11 JC11 JE11 JG11 JI11 JK11 JM11 JO11 JQ11 JS11 JU11 JW11 JY11 KA11 KC11 KE11 KG11 KI11 KK11 KM11 KO11 KQ11 KS11 KU11 KW11 KY11 LA11 LC11 LE11 LG11 LI11 G13 I13 K13 M13 O13 Q13 S13 U13 W13 Y13 AA13 AC13 AE13 AG13 AI13 AK13 AM13 AO13 AQ13 AS13 AU13 AW13 AY13 BA13 BC13 BE13 BG13 BI13 BK13 BM13 BO13 BQ13 BS13 BU13 BW13 BY13 CA13 CC13 CE13 CG13 CI13 CK13 CM13 CO13 CQ13 CS13 CU13 CW13 CY13 DA13 DC13 DE13 DG13 DI13 DK13 DM13 DO13 DQ13 DS13 DU13 DW13 DY13 EA13 EC13 EE13 EG13 EI13 EK13 EM13 EO13 EQ13 ES13 EU13 EW13 EY13 FA13 FC13 FE13 FG13 FI13 FK13 FM13 FO13 FQ13 FS13 FU13 FW13 FY13 GA13 GC13 GE13 GG13 GI13 GK13 GM13 GO13 GQ13 GS13 GU13 GW13 GY13 HA13 HC13 HE13 HG13 HI13 HK13 HM13 HO13 HQ13 HS13 HU13 HW13 HY13 IA13 IC13 IE13 IG13 II13 IK13 IM13 IO13 IQ13 IS13 IU13 IW13 IY13 JA13 JC13 JE13 JG13 JI13 JK13 JM13 JO13 JQ13 JS13 JU13 JW13 JY13 KA13 KC13 KE13 KG13 KI13 KK13 KM13 KO13 KQ13 KS13 KU13 KW13 KY13 LA13 LC13 LE13 LG13 LI13 G15 I15 K15 M15 O15 Q15 S15 U15 W15 Y15 AA15 AC15 AE15 AG15 AI15 AK15 AM15 AO15 AQ15 AS15 AU15 AW15 AY15 BA15 BC15 BE15 BG15 BI15 BK15 BM15 BO15 BQ15 BS15 BU15 BW15 BY15 CA15 CC15 CE15 CG15 CI15 CK15 CM15 CO15 CQ15 CS15 CU15 CW15 CY15 DA15 DC15 DE15 DG15 DI15 DK15 DM15 DO15 DQ15 DS15 DU15 DW15 DY15 EA15 EC15 EE15 EG15 EI15 EK15 EM15 EO15 EQ15 ES15 EU15 EW15 EY15 FA15 FC15 FE15 FG15 FI15 FK15 FM15 FO15 FQ15 FS15 FU15 FW15 FY15 GA15 GC15 GE15 GG15 GI15 GK15 GM15 GO15 GQ15 GS15 GU15 GW15 GY15 HA15 HC15 HE15 HG15 HI15 HK15 HM15 HO15 HQ15 HS15 HU15 HW15 HY15 IA15 IC15 IE15 IG15 II15 IK15 IM15 IO15 IQ15 IS15 IU15 IW15 IY15 JA15 JC15 JE15 JG15 JI15 JK15 JM15 JO15 JQ15 JS15 JU15 JW15 JY15 KA15 KC15 KE15 KG15 KI15 KK15 KM15 KO15 KQ15 KS15 KU15 KW15 KY15 LA15 LC15 LE15 LG15 LI15 G17 I17 K17 M17 O17 Q17 S17 U17 W17 Y17 AA17 AC17 AE17 AG17 AI17 AK17 AM17 AO17 AQ17 AS17 AU17 AW17 AY17 BA17 BC17 BE17 BG17 BI17 BK17 BM17 BO17 BQ17 BS17 BU17 BW17 BY17 CA17 CC17 CE17 CG17 CI17 CK17 CM17 CO17 CQ17 CS17 CU17 CW17 CY17 DA17 DC17 DE17 DG17 DI17 DK17 DM17 DO17 DQ17 DS17 DU17 DW17 DY17 EA17 EC17 EE17 EG17 EI17 EK17 EM17 EO17 EQ17 ES17 EU17 EW17 EY17 FA17 FC17 FE17 FG17 FI17 FK17 FM17 FO17 FQ17 FS17 FU17 FW17 FY17 GA17 GC17 GE17 GG17 GI17 GK17 GM17 GO17 GQ17 GS17 GU17 GW17 GY17 HA17 HC17 HE17 HG17 HI17 HK17 HM17 HO17 HQ17 HS17 HU17 HW17 HY17 IA17 IC17 IE17 IG17 II17 IK17 IM17 IO17 IQ17 IS17 IU17 IW17 IY17 JA17 JC17 JE17 JG17 JI17 JK17 JM17 JO17 JQ17 JS17 JU17 JW17 JY17 KA17 KC17 KE17 KG17 KI17 KK17 KM17 KO17 KQ17 KS17 KU17 KW17 KY17 LA17 LC17 LE17 LG17 LI17 G19 I19 K19 M19 O19 Q19 S19 U19 W19 Y19 AA19 AC19 AE19 AG19 AI19 AK19 AM19 AO19 AQ19 AS19 AU19 AW19 AY19 BA19 BC19 BE19 BG19 BI19 BK19 BM19 BO19 BQ19 BS19 BU19 BW19 BY19 CA19 CC19 CE19 CG19 CI19 CK19 CM19 CO19 CQ19 CS19 CU19 CW19 CY19 DA19 DC19 DE19 DG19 DI19 DK19 DM19 DO19 DQ19 DS19 DU19 DW19 DY19 EA19 EC19 EE19 EG19 EI19 EK19 EM19 EO19 EQ19 ES19 EU19 EW19 EY19 FA19 FC19 FE19 FG19 FI19 FK19 FM19 FO19 FQ19 FS19 FU19 FW19 FY19 GA19 GC19 GE19 GG19 GI19 GK19 GM19 GO19 GQ19 GS19 GU19 GW19 GY19 HA19 HC19 HE19 HG19 HI19 HK19 HM19 HO19 HQ19 HS19 HU19 HW19 HY19 IA19 IC19 IE19 IG19 II19 IK19 IM19 IO19 IQ19 IS19 IU19 IW19 IY19 JA19 JC19 JE19 JG19 JI19 JK19 JM19 JO19 JQ19 JS19 JU19 JW19 JY19 KA19 KC19 KE19 KG19 KI19 KK19 KM19 KO19 KQ19 KS19 KU19 KW19 KY19 LA19 LC19 LE19 LG19 LI19">
+  <conditionalFormatting sqref="C3 C5 C7 C9 C11 C13 C15 C17 C19 LI19 LG19 LE19 LC19 LA19 KY19 KW19 KU19 KS19 KQ19 KO19 JG19 JE19 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DC3 DE3 DG3 DI3 DK3 DM3 DO3 DQ3 DS3 DU3 DW3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KM19 KK19 JC19 JA19 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DC5 DE5 DG5 DI5 DK5 DM5 DO5 DQ5 DS5 DU5 DW5 DY5 EA5 EC5 EE5 EG5 EI5 EK5 EM5 EO5 EQ5 ES5 EU5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 KI5 KK5 KM5 KO5 KQ5 KS5 KU5 KW5 KY5 LA5 LC5 LE5 LG5 LI5 KI19 KG19 IY19 IW19 O7 Q7 S7 U7 W7 Y7 AA7 AC7 AE7 AG7 AI7 AK7 AM7 AO7 AQ7 AS7 AU7 AW7 AY7 BA7 BC7 BE7 BG7 BI7 BK7 BM7 BO7 BQ7 BS7 BU7 BW7 BY7 CA7 CC7 CE7 CG7 CI7 CK7 CM7 CO7 CQ7 CS7 CU7 CW7 CY7 DA7 DC7 DE7 DG7 DI7 DK7 DM7 DO7 DQ7 DS7 DU7 DW7 DY7 EA7 EC7 EE7 EG7 EI7 EK7 EM7 EO7 EQ7 ES7 EU7 EW7 EY7 FA7 FC7 FE7 FG7 FI7 FK7 FM7 FO7 FQ7 FS7 FU7 FW7 FY7 GA7 GC7 GE7 GG7 GI7 GK7 GM7 GO7 GQ7 GS7 GU7 GW7 GY7 HA7 HC7 HE7 HG7 HI7 HK7 HM7 HO7 HQ7 HS7 HU7 HW7 HY7 IA7 IC7 IE7 IG7 II7 IK7 IM7 IO7 IQ7 IS7 IU7 IW7 IY7 JA7 JC7 JE7 JG7 JI7 JK7 JM7 JO7 JQ7 JS7 JU7 JW7 JY7 KA7 KC7 KE7 KG7 KI7 KK7 KM7 KO7 KQ7 KS7 KU7 KW7 KY7 LA7 LC7 LE7 LG7 LI7 KE19 KC19 IU19 IS19 O9 Q9 S9 U9 W9 Y9 AA9 AC9 AE9 AG9 AI9 AK9 AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BW9 BY9 CA9 CC9 CE9 CG9 CI9 CK9 CM9 CO9 CQ9 CS9 CU9 CW9 CY9 DA9 DC9 DE9 DG9 DI9 DK9 DM9 DO9 DQ9 DS9 DU9 DW9 DY9 EA9 EC9 EE9 EG9 EI9 EK9 EM9 EO9 EQ9 ES9 EU9 EW9 EY9 FA9 FC9 FE9 FG9 FI9 FK9 FM9 FO9 FQ9 FS9 FU9 FW9 FY9 GA9 GC9 GE9 GG9 GI9 GK9 GM9 GO9 GQ9 GS9 GU9 GW9 GY9 HA9 HC9 HE9 HG9 HI9 HK9 HM9 HO9 HQ9 HS9 HU9 HW9 HY9 IA9 IC9 IE9 IG9 II9 IK9 IM9 IO9 IQ9 IS9 IU9 IW9 IY9 JA9 JC9 JE9 JG9 JI9 JK9 JM9 JO9 JQ9 JS9 JU9 JW9 JY9 KA9 KC9 KE9 KG9 KI9 KK9 KM9 KO9 KQ9 KS9 KU9 KW9 KY9 LA9 LC9 LE9 LG9 LI9 KA19 JY19 IQ19 IO19 O11 Q11 S11 U11 W11 Y11 AA11 AC11 AE11 AG11 AI11 AK11 AM11 AO11 AQ11 AS11 AU11 AW11 AY11 BA11 BC11 BE11 BG11 BI11 BK11 BM11 BO11 BQ11 BS11 BU11 BW11 BY11 CA11 CC11 CE11 CG11 CI11 CK11 CM11 CO11 CQ11 CS11 CU11 CW11 CY11 DA11 DC11 DE11 DG11 DI11 DK11 DM11 DO11 DQ11 DS11 DU11 DW11 DY11 EA11 EC11 EE11 EG11 EI11 EK11 EM11 EO11 EQ11 ES11 EU11 EW11 EY11 FA11 FC11 FE11 FG11 FI11 FK11 FM11 FO11 FQ11 FS11 FU11 FW11 FY11 GA11 GC11 GE11 GG11 GI11 GK11 GM11 GO11 GQ11 GS11 GU11 GW11 GY11 HA11 HC11 HE11 HG11 HI11 HK11 HM11 HO11 HQ11 HS11 HU11 HW11 HY11 IA11 IC11 IE11 IG11 II11 IK11 IM11 IO11 IQ11 IS11 IU11 IW11 IY11 JA11 JC11 JE11 JG11 JI11 JK11 JM11 JO11 JQ11 JS11 JU11 JW11 JY11 KA11 KC11 KE11 KG11 KI11 KK11 KM11 KO11 KQ11 KS11 KU11 KW11 KY11 LA11 LC11 LE11 LG11 LI11 JW19 JU19 IM19 IK19 O13 Q13 S13 U13 W13 Y13 AA13 AC13 AE13 AG13 AI13 AK13 AM13 AO13 AQ13 AS13 AU13 AW13 AY13 BA13 BC13 BE13 BG13 BI13 BK13 BM13 BO13 BQ13 BS13 BU13 BW13 BY13 CA13 CC13 CE13 CG13 CI13 CK13 CM13 CO13 CQ13 CS13 CU13 CW13 CY13 DA13 DC13 DE13 DG13 DI13 DK13 DM13 DO13 DQ13 DS13 DU13 DW13 DY13 EA13 EC13 EE13 EG13 EI13 EK13 EM13 EO13 EQ13 ES13 EU13 EW13 EY13 FA13 FC13 FE13 FG13 FI13 FK13 FM13 FO13 FQ13 FS13 FU13 FW13 FY13 GA13 GC13 GE13 GG13 GI13 GK13 GM13 GO13 GQ13 GS13 GU13 GW13 GY13 HA13 HC13 HE13 HG13 HI13 HK13 HM13 HO13 HQ13 HS13 HU13 HW13 HY13 IA13 IC13 IE13 IG13 II13 IK13 IM13 IO13 IQ13 IS13 IU13 IW13 IY13 JA13 JC13 JE13 JG13 JI13 JK13 JM13 JO13 JQ13 JS13 JU13 JW13 JY13 KA13 KC13 KE13 KG13 KI13 KK13 KM13 KO13 KQ13 KS13 KU13 KW13 KY13 LA13 LC13 LE13 LG13 LI13 JS19 JQ19 II19 IG19 O15 Q15 S15 U15 W15 Y15 AA15 AC15 AE15 AG15 AI15 AK15 AM15 AO15 AQ15 AS15 AU15 AW15 AY15 BA15 BC15 BE15 BG15 BI15 BK15 BM15 BO15 BQ15 BS15 BU15 BW15 BY15 CA15 CC15 CE15 CG15 CI15 CK15 CM15 CO15 CQ15 CS15 CU15 CW15 CY15 DA15 DC15 DE15 DG15 DI15 DK15 DM15 DO15 DQ15 DS15 DU15 DW15 DY15 EA15 EC15 EE15 EG15 EI15 EK15 EM15 EO15 EQ15 ES15 EU15 EW15 EY15 FA15 FC15 FE15 FG15 FI15 FK15 FM15 FO15 FQ15 FS15 FU15 FW15 FY15 GA15 GC15 GE15 GG15 GI15 GK15 GM15 GO15 GQ15 GS15 GU15 GW15 GY15 HA15 HC15 HE15 HG15 HI15 HK15 HM15 HO15 HQ15 HS15 HU15 HW15 HY15 IA15 IC15 IE15 IG15 II15 IK15 IM15 IO15 IQ15 IS15 IU15 IW15 IY15 JA15 JC15 JE15 JG15 JI15 JK15 JM15 JO15 JQ15 JS15 JU15 JW15 JY15 KA15 KC15 KE15 KG15 KI15 KK15 KM15 KO15 KQ15 KS15 KU15 KW15 KY15 LA15 LC15 LE15 LG15 LI15 JO19 JM19 IE19 IC19 O17 Q17 S17 U17 W17 Y17 AA17 AC17 AE17 AG17 AI17 AK17 AM17 AO17 AQ17 AS17 AU17 AW17 AY17 BA17 BC17 BE17 BG17 BI17 BK17 BM17 BO17 BQ17 BS17 BU17 BW17 BY17 CA17 CC17 CE17 CG17 CI17 CK17 CM17 CO17 CQ17 CS17 CU17 CW17 CY17 DA17 DC17 DE17 DG17 DI17 DK17 DM17 DO17 DQ17 DS17 DU17 DW17 DY17 EA17 EC17 EE17 EG17 EI17 EK17 EM17 EO17 EQ17 ES17 EU17 EW17 EY17 FA17 FC17 FE17 FG17 FI17 FK17 FM17 FO17 FQ17 FS17 FU17 FW17 FY17 GA17 GC17 GE17 GG17 GI17 GK17 GM17 GO17 GQ17 GS17 GU17 GW17 GY17 HA17 HC17 HE17 HG17 HI17 HK17 HM17 HO17 HQ17 HS17 HU17 HW17 HY17 IA17 IC17 IE17 IG17 II17 IK17 IM17 IO17 IQ17 IS17 IU17 IW17 IY17 JA17 JC17 JE17 JG17 JI17 JK17 JM17 JO17 JQ17 JS17 JU17 JW17 JY17 KA17 KC17 KE17 KG17 KI17 KK17 KM17 KO17 KQ17 KS17 KU17 KW17 KY17 LA17 LC17 LE17 LG17 LI17 JK19 JI19 IA19 HY19 O19 Q19 S19 U19 W19 Y19 AA19 AC19 AE19 AG19 AI19 AK19 AM19 AO19 AQ19 AS19 AU19 AW19 AY19 BA19 BC19 BE19 BG19 BI19 BK19 BM19 BO19 BQ19 BS19 BU19 BW19 BY19 CA19 CC19 CE19 CG19 CI19 CK19 CM19 CO19 CQ19 CS19 CU19 CW19 CY19 DA19 DC19 DE19 DG19 DI19 DK19 DM19 DO19 DQ19 DS19 DU19 DW19 DY19 EA19 EC19 EE19 EG19 EI19 EK19 EM19 EO19 EQ19 ES19 EU19 EW19 EY19 FA19 FC19 FE19 FG19 FI19 FK19 FM19 FO19 FQ19 FS19 FU19 FW19 FY19 GA19 GC19 GE19 GG19 GI19 GK19 GM19 GO19 GQ19 GS19 GU19 GW19 GY19 HA19 HC19 HE19 HG19 HI19 HK19 HM19 HO19 HQ19 HS19 HU19 HW19 M19 K19 M17 K17 M15 K15 M13 K13 M11 K11 M9 K9 M7 K7 M5 K5 M3 K3 I9 I7 I19 I17 I15 I13 I11 I5 I3 E3 G3 E5 G5 E11 G11 E13 G13 E15 G15 E17 G17 E19 G19 E7 G7 E9 G9">
     <cfRule type="containsBlanks" dxfId="1" priority="1">
       <formula>LEN(TRIM(C3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C20 E3:E20 G3:G20 I3:I20 K3:K20 M3:M20 O3:O20 Q3:Q20 S3:S20 U3:U20 W3:W20 Y3:Y20 AA3:AA20 AC3:AC20 AE3:AE20 AG3:AG20 AI3:AI20 AK3:AK20 AM3:AM20 AO3:AO20 AQ3:AQ20 AS3:AS20 AU3:AU20 AW3:AW20 AY3:AY20 BA3:BA20 BC3:BC20 BE3:BE20 BG3:BG20 BI3:BI20 BK3:BK20 BM3:BM20 BO3:BO20 BQ3:BQ20 BS3:BS20 BU3:BU20 BW3:BW20 BY3:BY20 CA3:CA20 CC3:CC20 CE3:CE20 CG3:CG20 CI3:CI20 CK3:CK20 CM3:CM20 CO3:CO20 CQ3:CQ20 CS3:CS20 CU3:CU20 CW3:CW20 CY3:CY20 DA3:DA20 DC3:DC20 DE3:DE20 DG3:DG20 DI3:DI20 DK3:DK20 DM3:DM20 DO3:DO20 DQ3:DQ20 DS3:DS20 DU3:DU20 DW3:DW20 DY3:DY20 EA3:EA20 EC3:EC20 EE3:EE20 EG3:EG20 EI3:EI20 EK3:EK20 EM3:EM20 EO3:EO20 EQ3:EQ20 ES3:ES20 EU3:EU20 EW3:EW20 EY3:EY20 FA3:FA20 FC3:FC20 FE3:FE20 FG3:FG20 FI3:FI20 FK3:FK20 FM3:FM20 FO3:FO20 FQ3:FQ20 FS3:FS20 FU3:FU20 FW3:FW20 FY3:FY20 GA3:GA20 GC3:GC20 GE3:GE20 GG3:GG20 GI3:GI20 GK3:GK20 GM3:GM20 GO3:GO20 GQ3:GQ20 GS3:GS20 GU3:GU20 GW3:GW20 GY3:GY20 HA3:HA20 HC3:HC20 HE3:HE20 HG3:HG20 HI3:HI20 HK3:HK20 HM3:HM20 HO3:HO20 HQ3:HQ20 HS3:HS20 HU3:HU20 HW3:HW20 HY3:HY20 IA3:IA20 IC3:IC20 IE3:IE20 IG3:IG20 II3:II20 IK3:IK20 IM3:IM20 IO3:IO20 IQ3:IQ20 IS3:IS20 IU3:IU20 IW3:IW20 IY3:IY20 JA3:JA20 JC3:JC20 JE3:JE20 JG3:JG20 JI3:JI20 JK3:JK20 JM3:JM20 JO3:JO20 JQ3:JQ20 JS3:JS20 JU3:JU20 JW3:JW20 JY3:JY20 KA3:KA20 KC3:KC20 KE3:KE20 KG3:KG20 KI3:KI20 KK3:KK20 KM3:KM20 KO3:KO20 KQ3:KQ20 KS3:KS20 KU3:KU20 KW3:KW20 KY3:KY20 LA3:LA20 LC3:LC20 LE3:LE20 LG3:LG20 LI3:LI20">
+  <conditionalFormatting sqref="C3:C20 E3:E20 LI3:LI20 G3:G20 LG3:LG20 I3:I20 LE3:LE20 K3:K20 LC3:LC20 M3:M20 LA3:LA20 O3:O20 Q3:Q20 S3:S20 U3:U20 W3:W20 Y3:Y20 AA3:AA20 AC3:AC20 AE3:AE20 AG3:AG20 AI3:AI20 AK3:AK20 AM3:AM20 AO3:AO20 AQ3:AQ20 AS3:AS20 AU3:AU20 AW3:AW20 AY3:AY20 BA3:BA20 BC3:BC20 BE3:BE20 BG3:BG20 BI3:BI20 BK3:BK20 BM3:BM20 BO3:BO20 BQ3:BQ20 BS3:BS20 BU3:BU20 BW3:BW20 BY3:BY20 CA3:CA20 CC3:CC20 CE3:CE20 CG3:CG20 CI3:CI20 CK3:CK20 CM3:CM20 CO3:CO20 CQ3:CQ20 CS3:CS20 CU3:CU20 CW3:CW20 CY3:CY20 DA3:DA20 DC3:DC20 DE3:DE20 DG3:DG20 DI3:DI20 DK3:DK20 DM3:DM20 DO3:DO20 DQ3:DQ20 DS3:DS20 DU3:DU20 DW3:DW20 DY3:DY20 EA3:EA20 EC3:EC20 EE3:EE20 EG3:EG20 EI3:EI20 EK3:EK20 EM3:EM20 EO3:EO20 EQ3:EQ20 ES3:ES20 EU3:EU20 EW3:EW20 EY3:EY20 FA3:FA20 FC3:FC20 FE3:FE20 FG3:FG20 FI3:FI20 FK3:FK20 FM3:FM20 FO3:FO20 FQ3:FQ20 FS3:FS20 FU3:FU20 FW3:FW20 FY3:FY20 GA3:GA20 GC3:GC20 GE3:GE20 GG3:GG20 GI3:GI20 GK3:GK20 GM3:GM20 GO3:GO20 GQ3:GQ20 GS3:GS20 GU3:GU20 GW3:GW20 GY3:GY20 HA3:HA20 HC3:HC20 HE3:HE20 HG3:HG20 HI3:HI20 HK3:HK20 HM3:HM20 HO3:HO20 HQ3:HQ20 HS3:HS20 HU3:HU20 HW3:HW20 HY3:HY20 IA3:IA20 IC3:IC20 IE3:IE20 IG3:IG20 II3:II20 IK3:IK20 IM3:IM20 IO3:IO20 IQ3:IQ20 IS3:IS20 IU3:IU20 IW3:IW20 IY3:IY20 JA3:JA20 JC3:JC20 JE3:JE20 JG3:JG20 JI3:JI20 JK3:JK20 JM3:JM20 JO3:JO20 JQ3:JQ20 JS3:JS20 JU3:JU20 JW3:JW20 JY3:JY20 KA3:KA20 KC3:KC20 KE3:KE20 KG3:KG20 KI3:KI20 KK3:KK20 KM3:KM20 KO3:KO20 KQ3:KQ20 KS3:KS20 KU3:KU20 KW3:KW20 KY3:KY20">
     <cfRule type="containsText" dxfId="2" priority="2" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3 D3 F3 H3 J3 L3 N3 P3 R3 T3 V3 X3 Z3 AB3 AD3 AF3 AH3 AJ3 AL3 AN3 AP3 AR3 AT3 AV3 AX3 AZ3 BB3 BD3 BF3 BH3 BJ3 BL3 BN3 BP3 BR3 BT3 BV3 BX3 BZ3 CB3 CD3 CF3 CH3 CJ3 CL3 CN3 CP3 CR3 CT3 CV3 CX3 CZ3 DB3 DD3 DF3 DH3 DJ3 DL3 DN3 DP3 DR3 DT3 DV3 DX3 DZ3 EB3 ED3 EF3 EH3 EJ3 EL3 EN3 EP3 ER3 ET3 EV3 EX3 EZ3 FB3 FD3 FF3 FH3 FJ3 FL3 FN3 FP3 FR3 FT3 FV3 FX3 FZ3 GB3 GD3 GF3 GH3 GJ3 GL3 GN3 GP3 GR3 GT3 GV3 GX3 GZ3 HB3 HD3 HF3 HH3 HJ3 HL3 HN3 HP3 HR3 HT3 HV3 HX3 HZ3 IB3 ID3 IF3 IH3 IJ3 IL3 IN3 IP3 IR3 IT3 IV3 IX3 IZ3 JB3 JD3 JF3 JH3 JJ3 JL3 JN3 JP3 JR3 JT3 JV3 JX3 JZ3 KB3 KD3 KF3 KH3 KJ3 KL3 KN3 KP3 KR3 KT3 KV3 KX3 KZ3 LB3 LD3 LF3 LH3 B4 D4 F4 H4 J4 L4 N4 P4 R4 T4 V4 X4 Z4 AB4 AD4 AF4 AH4 AJ4 AL4 AN4 AP4 AR4 AT4 AV4 AX4 AZ4 BB4 BD4 BF4 BH4 BJ4 BL4 BN4 BP4 BR4 BT4 BV4 BX4 BZ4 CB4 CD4 CF4 CH4 CJ4 CL4 CN4 CP4 CR4 CT4 CV4 CX4 CZ4 DB4 DD4 DF4 DH4 DJ4 DL4 DN4 DP4 DR4 DT4 DV4 DX4 DZ4 EB4 ED4 EF4 EH4 EJ4 EL4 EN4 EP4 ER4 ET4 EV4 EX4 EZ4 FB4 FD4 FF4 FH4 FJ4 FL4 FN4 FP4 FR4 FT4 FV4 FX4 FZ4 GB4 GD4 GF4 GH4 GJ4 GL4 GN4 GP4 GR4 GT4 GV4 GX4 GZ4 HB4 HD4 HF4 HH4 HJ4 HL4 HN4 HP4 HR4 HT4 HV4 HX4 HZ4 IB4 ID4 IF4 IH4 IJ4 IL4 IN4 IP4 IR4 IT4 IV4 IX4 IZ4 JB4 JD4 JF4 JH4 JJ4 JL4 JN4 JP4 JR4 JT4 JV4 JX4 JZ4 KB4 KD4 KF4 KH4 KJ4 KL4 KN4 KP4 KR4 KT4 KV4 KX4 KZ4 LB4 LD4 LF4 LH4 B5 D5 F5 H5 J5 L5 N5 P5 R5 T5 V5 X5 Z5 AB5 AD5 AF5 AH5 AJ5 AL5 AN5 AP5 AR5 AT5 AV5 AX5 AZ5 BB5 BD5 BF5 BH5 BJ5 BL5 BN5 BP5 BR5 BT5 BV5 BX5 BZ5 CB5 CD5 CF5 CH5 CJ5 CL5 CN5 CP5 CR5 CT5 CV5 CX5 CZ5 DB5 DD5 DF5 DH5 DJ5 DL5 DN5 DP5 DR5 DT5 DV5 DX5 DZ5 EB5 ED5 EF5 EH5 EJ5 EL5 EN5 EP5 ER5 ET5 EV5 EX5 EZ5 FB5 FD5 FF5 FH5 FJ5 FL5 FN5 FP5 FR5 FT5 FV5 FX5 FZ5 GB5 GD5 GF5 GH5 GJ5 GL5 GN5 GP5 GR5 GT5 GV5 GX5 GZ5 HB5 HD5 HF5 HH5 HJ5 HL5 HN5 HP5 HR5 HT5 HV5 HX5 HZ5 IB5 ID5 IF5 IH5 IJ5 IL5 IN5 IP5 IR5 IT5 IV5 IX5 IZ5 JB5 JD5 JF5 JH5 JJ5 JL5 JN5 JP5 JR5 JT5 JV5 JX5 JZ5 KB5 KD5 KF5 KH5 KJ5 KL5 KN5 KP5 KR5 KT5 KV5 KX5 KZ5 LB5 LD5 LF5 LH5 B6 D6 F6 H6 J6 L6 N6 P6 R6 T6 V6 X6 Z6 AB6 AD6 AF6 AH6 AJ6 AL6 AN6 AP6 AR6 AT6 AV6 AX6 AZ6 BB6 BD6 BF6 BH6 BJ6 BL6 BN6 BP6 BR6 BT6 BV6 BX6 BZ6 CB6 CD6 CF6 CH6 CJ6 CL6 CN6 CP6 CR6 CT6 CV6 CX6 CZ6 DB6 DD6 DF6 DH6 DJ6 DL6 DN6 DP6 DR6 DT6 DV6 DX6 DZ6 EB6 ED6 EF6 EH6 EJ6 EL6 EN6 EP6 ER6 ET6 EV6 EX6 EZ6 FB6 FD6 FF6 FH6 FJ6 FL6 FN6 FP6 FR6 FT6 FV6 FX6 FZ6 GB6 GD6 GF6 GH6 GJ6 GL6 GN6 GP6 GR6 GT6 GV6 GX6 GZ6 HB6 HD6 HF6 HH6 HJ6 HL6 HN6 HP6 HR6 HT6 HV6 HX6 HZ6 IB6 ID6 IF6 IH6 IJ6 IL6 IN6 IP6 IR6 IT6 IV6 IX6 IZ6 JB6 JD6 JF6 JH6 JJ6 JL6 JN6 JP6 JR6 JT6 JV6 JX6 JZ6 KB6 KD6 KF6 KH6 KJ6 KL6 KN6 KP6 KR6 KT6 KV6 KX6 KZ6 LB6 LD6 LF6 LH6 B7 D7 F7 H7 J7 L7 N7 P7 R7 T7 V7 X7 Z7 AB7 AD7 AF7 AH7 AJ7 AL7 AN7 AP7 AR7 AT7 AV7 AX7 AZ7 BB7 BD7 BF7 BH7 BJ7 BL7 BN7 BP7 BR7 BT7 BV7 BX7 BZ7 CB7 CD7 CF7 CH7 CJ7 CL7 CN7 CP7 CR7 CT7 CV7 CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7 DV7 DX7 DZ7 EB7 ED7 EF7 EH7 EJ7 EL7 EN7 EP7 ER7 ET7 EV7 EX7 EZ7 FB7 FD7 FF7 FH7 FJ7 FL7 FN7 FP7 FR7 FT7 FV7 FX7 FZ7 GB7 GD7 GF7 GH7 GJ7 GL7 GN7 GP7 GR7 GT7 GV7 GX7 GZ7 HB7 HD7 HF7 HH7 HJ7 HL7 HN7 HP7 HR7 HT7 HV7 HX7 HZ7 IB7 ID7 IF7 IH7 IJ7 IL7 IN7 IP7 IR7 IT7 IV7 IX7 IZ7 JB7 JD7 JF7 JH7 JJ7 JL7 JN7 JP7 JR7 JT7 JV7 JX7 JZ7 KB7 KD7 KF7 KH7 KJ7 KL7 KN7 KP7 KR7 KT7 KV7 KX7 KZ7 LB7 LD7 LF7 LH7 B8 D8 F8 H8 J8 L8 N8 P8 R8 T8 V8 X8 Z8 AB8 AD8 AF8 AH8 AJ8 AL8 AN8 AP8 AR8 AT8 AV8 AX8 AZ8 BB8 BD8 BF8 BH8 BJ8 BL8 BN8 BP8 BR8 BT8 BV8 BX8 BZ8 CB8 CD8 CF8 CH8 CJ8 CL8 CN8 CP8 CR8 CT8 CV8 CX8 CZ8 DB8 DD8 DF8 DH8 DJ8 DL8 DN8 DP8 DR8 DT8 DV8 DX8 DZ8 EB8 ED8 EF8 EH8 EJ8 EL8 EN8 EP8 ER8 ET8 EV8 EX8 EZ8 FB8 FD8 FF8 FH8 FJ8 FL8 FN8 FP8 FR8 FT8 FV8 FX8 FZ8 GB8 GD8 GF8 GH8 GJ8 GL8 GN8 GP8 GR8 GT8 GV8 GX8 GZ8 HB8 HD8 HF8 HH8 HJ8 HL8 HN8 HP8 HR8 HT8 HV8 HX8 HZ8 IB8 ID8 IF8 IH8 IJ8 IL8 IN8 IP8 IR8 IT8 IV8 IX8 IZ8 JB8 JD8 JF8 JH8 JJ8 JL8 JN8 JP8 JR8 JT8 JV8 JX8 JZ8 KB8 KD8 KF8 KH8 KJ8 KL8 KN8 KP8 KR8 KT8 KV8 KX8 KZ8 LB8 LD8 LF8 LH8 B9 D9 F9 H9 J9 L9 N9 P9 R9 T9 V9 X9 Z9 AB9 AD9 AF9 AH9 AJ9 AL9 AN9 AP9 AR9 AT9 AV9 AX9 AZ9 BB9 BD9 BF9 BH9 BJ9 BL9 BN9 BP9 BR9 BT9 BV9 BX9 BZ9 CB9 CD9 CF9 CH9 CJ9 CL9 CN9 CP9 CR9 CT9 CV9 CX9 CZ9 DB9 DD9 DF9 DH9 DJ9 DL9 DN9 DP9 DR9 DT9 DV9 DX9 DZ9 EB9 ED9 EF9 EH9 EJ9 EL9 EN9 EP9 ER9 ET9 EV9 EX9 EZ9 FB9 FD9 FF9 FH9 FJ9 FL9 FN9 FP9 FR9 FT9 FV9 FX9 FZ9 GB9 GD9 GF9 GH9 GJ9 GL9 GN9 GP9 GR9 GT9 GV9 GX9 GZ9 HB9 HD9 HF9 HH9 HJ9 HL9 HN9 HP9 HR9 HT9 HV9 HX9 HZ9 IB9 ID9 IF9 IH9 IJ9 IL9 IN9 IP9 IR9 IT9 IV9 IX9 IZ9 JB9 JD9 JF9 JH9 JJ9 JL9 JN9 JP9 JR9 JT9 JV9 JX9 JZ9 KB9 KD9 KF9 KH9 KJ9 KL9 KN9 KP9 KR9 KT9 KV9 KX9 KZ9 LB9 LD9 LF9 LH9 B10 D10 F10 H10 J10 L10 N10 P10 R10 T10 V10 X10 Z10 AB10 AD10 AF10 AH10 AJ10 AL10 AN10 AP10 AR10 AT10 AV10 AX10 AZ10 BB10 BD10 BF10 BH10 BJ10 BL10 BN10 BP10 BR10 BT10 BV10 BX10 BZ10 CB10 CD10 CF10 CH10 CJ10 CL10 CN10 CP10 CR10 CT10 CV10 CX10 CZ10 DB10 DD10 DF10 DH10 DJ10 DL10 DN10 DP10 DR10 DT10 DV10 DX10 DZ10 EB10 ED10 EF10 EH10 EJ10 EL10 EN10 EP10 ER10 ET10 EV10 EX10 EZ10 FB10 FD10 FF10 FH10 FJ10 FL10 FN10 FP10 FR10 FT10 FV10 FX10 FZ10 GB10 GD10 GF10 GH10 GJ10 GL10 GN10 GP10 GR10 GT10 GV10 GX10 GZ10 HB10 HD10 HF10 HH10 HJ10 HL10 HN10 HP10 HR10 HT10 HV10 HX10 HZ10 IB10 ID10 IF10 IH10 IJ10 IL10 IN10 IP10 IR10 IT10 IV10 IX10 IZ10 JB10 JD10 JF10 JH10 JJ10 JL10 JN10 JP10 JR10 JT10 JV10 JX10 JZ10 KB10 KD10 KF10 KH10 KJ10 KL10 KN10 KP10 KR10 KT10 KV10 KX10 KZ10 LB10 LD10 LF10 LH10 B11 D11 F11 H11 J11 L11 N11 P11 R11 T11 V11 X11 Z11 AB11 AD11 AF11 AH11 AJ11 AL11 AN11 AP11 AR11 AT11 AV11 AX11 AZ11 BB11 BD11 BF11 BH11 BJ11 BL11 BN11 BP11 BR11 BT11 BV11 BX11 BZ11 CB11 CD11 CF11 CH11 CJ11 CL11 CN11 CP11 CR11 CT11 CV11 CX11 CZ11 DB11 DD11 DF11 DH11 DJ11 DL11 DN11 DP11 DR11 DT11 DV11 DX11 DZ11 EB11 ED11 EF11 EH11 EJ11 EL11 EN11 EP11 ER11 ET11 EV11 EX11 EZ11 FB11 FD11 FF11 FH11 FJ11 FL11 FN11 FP11 FR11 FT11 FV11 FX11 FZ11 GB11 GD11 GF11 GH11 GJ11 GL11 GN11 GP11 GR11 GT11 GV11 GX11 GZ11 HB11 HD11 HF11 HH11 HJ11 HL11 HN11 HP11 HR11 HT11 HV11 HX11 HZ11 IB11 ID11 IF11 IH11 IJ11 IL11 IN11 IP11 IR11 IT11 IV11 IX11 IZ11 JB11 JD11 JF11 JH11 JJ11 JL11 JN11 JP11 JR11 JT11 JV11 JX11 JZ11 KB11 KD11 KF11 KH11 KJ11 KL11 KN11 KP11 KR11 KT11 KV11 KX11 KZ11 LB11 LD11 LF11 LH11 B12 D12 F12 H12 J12 L12 N12 P12 R12 T12 V12 X12 Z12 AB12 AD12 AF12 AH12 AJ12 AL12 AN12 AP12 AR12 AT12 AV12 AX12 AZ12 BB12 BD12 BF12 BH12 BJ12 BL12 BN12 BP12 BR12 BT12 BV12 BX12 BZ12 CB12 CD12 CF12 CH12 CJ12 CL12 CN12 CP12 CR12 CT12 CV12 CX12 CZ12 DB12 DD12 DF12 DH12 DJ12 DL12 DN12 DP12 DR12 DT12 DV12 DX12 DZ12 EB12 ED12 EF12 EH12 EJ12 EL12 EN12 EP12 ER12 ET12 EV12 EX12 EZ12 FB12 FD12 FF12 FH12 FJ12 FL12 FN12 FP12 FR12 FT12 FV12 FX12 FZ12 GB12 GD12 GF12 GH12 GJ12 GL12 GN12 GP12 GR12 GT12 GV12 GX12 GZ12 HB12 HD12 HF12 HH12 HJ12 HL12 HN12 HP12 HR12 HT12 HV12 HX12 HZ12 IB12 ID12 IF12 IH12 IJ12 IL12 IN12 IP12 IR12 IT12 IV12 IX12 IZ12 JB12 JD12 JF12 JH12 JJ12 JL12 JN12 JP12 JR12 JT12 JV12 JX12 JZ12 KB12 KD12 KF12 KH12 KJ12 KL12 KN12 KP12 KR12 KT12 KV12 KX12 KZ12 LB12 LD12 LF12 LH12 B13 D13 F13 H13 J13 L13 N13 P13 R13 T13 V13 X13 Z13 AB13 AD13 AF13 AH13 AJ13 AL13 AN13 AP13 AR13 AT13 AV13 AX13 AZ13 BB13 BD13 BF13 BH13 BJ13 BL13 BN13 BP13 BR13 BT13 BV13 BX13 BZ13 CB13 CD13 CF13 CH13 CJ13 CL13 CN13 CP13 CR13 CT13 CV13 CX13 CZ13 DB13 DD13 DF13 DH13 DJ13 DL13 DN13 DP13 DR13 DT13 DV13 DX13 DZ13 EB13 ED13 EF13 EH13 EJ13 EL13 EN13 EP13 ER13 ET13 EV13 EX13 EZ13 FB13 FD13 FF13 FH13 FJ13 FL13 FN13 FP13 FR13 FT13 FV13 FX13 FZ13 GB13 GD13 GF13 GH13 GJ13 GL13 GN13 GP13 GR13 GT13 GV13 GX13 GZ13 HB13 HD13 HF13 HH13 HJ13 HL13 HN13 HP13 HR13 HT13 HV13 HX13 HZ13 IB13 ID13 IF13 IH13 IJ13 IL13 IN13 IP13 IR13 IT13 IV13 IX13 IZ13 JB13 JD13 JF13 JH13 JJ13 JL13 JN13 JP13 JR13 JT13 JV13 JX13 JZ13 KB13 KD13 KF13 KH13 KJ13 KL13 KN13 KP13 KR13 KT13 KV13 KX13 KZ13 LB13 LD13 LF13 LH13 B14 D14 F14 H14 J14 L14 N14 P14 R14 T14 V14 X14 Z14 AB14 AD14 AF14 AH14 AJ14 AL14 AN14 AP14 AR14 AT14 AV14 AX14 AZ14 BB14 BD14 BF14 BH14 BJ14 BL14 BN14 BP14 BR14 BT14 BV14 BX14 BZ14 CB14 CD14 CF14 CH14 CJ14 CL14 CN14 CP14 CR14 CT14 CV14 CX14 CZ14 DB14 DD14 DF14 DH14 DJ14 DL14 DN14 DP14 DR14 DT14 DV14 DX14 DZ14 EB14 ED14 EF14 EH14 EJ14 EL14 EN14 EP14 ER14 ET14 EV14 EX14 EZ14 FB14 FD14 FF14 FH14 FJ14 FL14 FN14 FP14 FR14 FT14 FV14 FX14 FZ14 GB14 GD14 GF14 GH14 GJ14 GL14 GN14 GP14 GR14 GT14 GV14 GX14 GZ14 HB14 HD14 HF14 HH14 HJ14 HL14 HN14 HP14 HR14 HT14 HV14 HX14 HZ14 IB14 ID14 IF14 IH14 IJ14 IL14 IN14 IP14 IR14 IT14 IV14 IX14 IZ14 JB14 JD14 JF14 JH14 JJ14 JL14 JN14 JP14 JR14 JT14 JV14 JX14 JZ14 KB14 KD14 KF14 KH14 KJ14 KL14 KN14 KP14 KR14 KT14 KV14 KX14 KZ14 LB14 LD14 LF14 LH14 B15 D15 F15 H15 J15 L15 N15 P15 R15 T15 V15 X15 Z15 AB15 AD15 AF15 AH15 AJ15 AL15 AN15 AP15 AR15 AT15 AV15 AX15 AZ15 BB15 BD15 BF15 BH15 BJ15 BL15 BN15 BP15 BR15 BT15 BV15 BX15 BZ15 CB15 CD15 CF15 CH15 CJ15 CL15 CN15 CP15 CR15 CT15 CV15 CX15 CZ15 DB15 DD15 DF15 DH15 DJ15 DL15 DN15 DP15 DR15 DT15 DV15 DX15 DZ15 EB15 ED15 EF15 EH15 EJ15 EL15 EN15 EP15 ER15 ET15 EV15 EX15 EZ15 FB15 FD15 FF15 FH15 FJ15 FL15 FN15 FP15 FR15 FT15 FV15 FX15 FZ15 GB15 GD15 GF15 GH15 GJ15 GL15 GN15 GP15 GR15 GT15 GV15 GX15 GZ15 HB15 HD15 HF15 HH15 HJ15 HL15 HN15 HP15 HR15 HT15 HV15 HX15 HZ15 IB15 ID15 IF15 IH15 IJ15 IL15 IN15 IP15 IR15 IT15 IV15 IX15 IZ15 JB15 JD15 JF15 JH15 JJ15 JL15 JN15 JP15 JR15 JT15 JV15 JX15 JZ15 KB15 KD15 KF15 KH15 KJ15 KL15 KN15 KP15 KR15 KT15 KV15 KX15 KZ15 LB15 LD15 LF15 LH15 B16 D16 F16 H16 J16 L16 N16 P16 R16 T16 V16 X16 Z16 AB16 AD16 AF16 AH16 AJ16 AL16 AN16 AP16 AR16 AT16 AV16 AX16 AZ16 BB16 BD16 BF16 BH16 BJ16 BL16 BN16 BP16 BR16 BT16 BV16 BX16 BZ16 CB16 CD16 CF16 CH16 CJ16 CL16 CN16 CP16 CR16 CT16 CV16 CX16 CZ16 DB16 DD16 DF16 DH16 DJ16 DL16 DN16 DP16 DR16 DT16 DV16 DX16 DZ16 EB16 ED16 EF16 EH16 EJ16 EL16 EN16 EP16 ER16 ET16 EV16 EX16 EZ16 FB16 FD16 FF16 FH16 FJ16 FL16 FN16 FP16 FR16 FT16 FV16 FX16 FZ16 GB16 GD16 GF16 GH16 GJ16 GL16 GN16 GP16 GR16 GT16 GV16 GX16 GZ16 HB16 HD16 HF16 HH16 HJ16 HL16 HN16 HP16 HR16 HT16 HV16 HX16 HZ16 IB16 ID16 IF16 IH16 IJ16 IL16 IN16 IP16 IR16 IT16 IV16 IX16 IZ16 JB16 JD16 JF16 JH16 JJ16 JL16 JN16 JP16 JR16 JT16 JV16 JX16 JZ16 KB16 KD16 KF16 KH16 KJ16 KL16 KN16 KP16 KR16 KT16 KV16 KX16 KZ16 LB16 LD16 LF16 LH16 B17 D17 F17 H17 J17 L17 N17 P17 R17 T17 V17 X17 Z17 AB17 AD17 AF17 AH17 AJ17 AL17 AN17 AP17 AR17 AT17 AV17 AX17 AZ17 BB17 BD17 BF17 BH17 BJ17 BL17 BN17 BP17 BR17 BT17 BV17 BX17 BZ17 CB17 CD17 CF17 CH17 CJ17 CL17 CN17 CP17 CR17 CT17 CV17 CX17 CZ17 DB17 DD17 DF17 DH17 DJ17 DL17 DN17 DP17 DR17 DT17 DV17 DX17 DZ17 EB17 ED17 EF17 EH17 EJ17 EL17 EN17 EP17 ER17 ET17 EV17 EX17 EZ17 FB17 FD17 FF17 FH17 FJ17 FL17 FN17 FP17 FR17 FT17 FV17 FX17 FZ17 GB17 GD17 GF17 GH17 GJ17 GL17 GN17 GP17 GR17 GT17 GV17 GX17 GZ17 HB17 HD17 HF17 HH17 HJ17 HL17 HN17 HP17 HR17 HT17 HV17 HX17 HZ17 IB17 ID17 IF17 IH17 IJ17 IL17 IN17 IP17 IR17 IT17 IV17 IX17 IZ17 JB17 JD17 JF17 JH17 JJ17 JL17 JN17 JP17 JR17 JT17 JV17 JX17 JZ17 KB17 KD17 KF17 KH17 KJ17 KL17 KN17 KP17 KR17 KT17 KV17 KX17 KZ17 LB17 LD17 LF17 LH17 B18 D18 F18 H18 J18 L18 N18 P18 R18 T18 V18 X18 Z18 AB18 AD18 AF18 AH18 AJ18 AL18 AN18 AP18 AR18 AT18 AV18 AX18 AZ18 BB18 BD18 BF18 BH18 BJ18 BL18 BN18 BP18 BR18 BT18 BV18 BX18 BZ18 CB18 CD18 CF18 CH18 CJ18 CL18 CN18 CP18 CR18 CT18 CV18 CX18 CZ18 DB18 DD18 DF18 DH18 DJ18 DL18 DN18 DP18 DR18 DT18 DV18 DX18 DZ18 EB18 ED18 EF18 EH18 EJ18 EL18 EN18 EP18 ER18 ET18 EV18 EX18 EZ18 FB18 FD18 FF18 FH18 FJ18 FL18 FN18 FP18 FR18 FT18 FV18 FX18 FZ18 GB18 GD18 GF18 GH18 GJ18 GL18 GN18 GP18 GR18 GT18 GV18 GX18 GZ18 HB18 HD18 HF18 HH18 HJ18 HL18 HN18 HP18 HR18 HT18 HV18 HX18 HZ18 IB18 ID18 IF18 IH18 IJ18 IL18 IN18 IP18 IR18 IT18 IV18 IX18 IZ18 JB18 JD18 JF18 JH18 JJ18 JL18 JN18 JP18 JR18 JT18 JV18 JX18 JZ18 KB18 KD18 KF18 KH18 KJ18 KL18 KN18 KP18 KR18 KT18 KV18 KX18 KZ18 LB18 LD18 LF18 LH18 B19 D19 F19 H19 J19 L19 N19 P19 R19 T19 V19 X19 Z19 AB19 AD19 AF19 AH19 AJ19 AL19 AN19 AP19 AR19 AT19 AV19 AX19 AZ19 BB19 BD19 BF19 BH19 BJ19 BL19 BN19 BP19 BR19 BT19 BV19 BX19 BZ19 CB19 CD19 CF19 CH19 CJ19 CL19 CN19 CP19 CR19 CT19 CV19 CX19 CZ19 DB19 DD19 DF19 DH19 DJ19 DL19 DN19 DP19 DR19 DT19 DV19 DX19 DZ19 EB19 ED19 EF19 EH19 EJ19 EL19 EN19 EP19 ER19 ET19 EV19 EX19 EZ19 FB19 FD19 FF19 FH19 FJ19 FL19 FN19 FP19 FR19 FT19 FV19 FX19 FZ19 GB19 GD19 GF19 GH19 GJ19 GL19 GN19 GP19 GR19 GT19 GV19 GX19 GZ19 HB19 HD19 HF19 HH19 HJ19 HL19 HN19 HP19 HR19 HT19 HV19 HX19 HZ19 IB19 ID19 IF19 IH19 IJ19 IL19 IN19 IP19 IR19 IT19 IV19 IX19 IZ19 JB19 JD19 JF19 JH19 JJ19 JL19 JN19 JP19 JR19 JT19 JV19 JX19 JZ19 KB19 KD19 KF19 KH19 KJ19 KL19 KN19 KP19 KR19 KT19 KV19 KX19 KZ19 LB19 LD19 LF19 LH19 B20 D20 F20 H20 J20 L20 N20 P20 R20 T20 V20 X20 Z20 AB20 AD20 AF20 AH20 AJ20 AL20 AN20 AP20 AR20 AT20 AV20 AX20 AZ20 BB20 BD20 BF20 BH20 BJ20 BL20 BN20 BP20 BR20 BT20 BV20 BX20 BZ20 CB20 CD20 CF20 CH20 CJ20 CL20 CN20 CP20 CR20 CT20 CV20 CX20 CZ20 DB20 DD20 DF20 DH20 DJ20 DL20 DN20 DP20 DR20 DT20 DV20 DX20 DZ20 EB20 ED20 EF20 EH20 EJ20 EL20 EN20 EP20 ER20 ET20 EV20 EX20 EZ20 FB20 FD20 FF20 FH20 FJ20 FL20 FN20 FP20 FR20 FT20 FV20 FX20 FZ20 GB20 GD20 GF20 GH20 GJ20 GL20 GN20 GP20 GR20 GT20 GV20 GX20 GZ20 HB20 HD20 HF20 HH20 HJ20 HL20 HN20 HP20 HR20 HT20 HV20 HX20 HZ20 IB20 ID20 IF20 IH20 IJ20 IL20 IN20 IP20 IR20 IT20 IV20 IX20 IZ20 JB20 JD20 JF20 JH20 JJ20 JL20 JN20 JP20 JR20 JT20 JV20 JX20 JZ20 KB20 KD20 KF20 KH20 KJ20 KL20 KN20 KP20 KR20 KT20 KV20 KX20 KZ20 LB20 LD20 LF20 LH20">
-      <formula1>数据!$A$1:$A$28</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3 D3 F3 B4 D4 F4 B5 D5 F5 B6 D6 F6 B7 D7 F7 B8 D8 F8 B9 D9 F9 B10 D10 F10 B11 D11 F11 B12 D12 F12 B13 D13 F13 B14 D14 F14 B15 D15 F15 B16 D16 F16 B17 D17 F17 B18 D18 F18 B19 D19 F19 B20 D20 F20 H20 J20 L20 H3:H19 J3:J19 L3:L19 N3:N20 P3:P20 R3:R20 T3:T20 V3:V20 X3:X20 Z3:Z20 AB3:AB20 AD3:AD20 AF3:AF20 AH3:AH20 AJ3:AJ20 AL3:AL20 AN3:AN20 AP3:AP20 AR3:AR20 AT3:AT20 AV3:AV20 AX3:AX20 AZ3:AZ20 BB3:BB20 BD3:BD20 BF3:BF20 BH3:BH20 BJ3:BJ20 BL3:BL20 BN3:BN20 BP3:BP20 BR3:BR20 BT3:BT20 BV3:BV20 BX3:BX20 BZ3:BZ20 CB3:CB20 CD3:CD20 CF3:CF20 CH3:CH20 CJ3:CJ20 CL3:CL20 CN3:CN20 CP3:CP20 CR3:CR20 CT3:CT20 CV3:CV20 CX3:CX20 CZ3:CZ20 DB3:DB20 DD3:DD20 DF3:DF20 DH3:DH20 DJ3:DJ20 DL3:DL20 DN3:DN20 DP3:DP20 DR3:DR20 DT3:DT20 DV3:DV20 DX3:DX20 DZ3:DZ20 EB3:EB20 ED3:ED20 EF3:EF20 EH3:EH20 EJ3:EJ20 EL3:EL20 EN3:EN20 EP3:EP20 ER3:ER20 ET3:ET20 EV3:EV20 EX3:EX20 EZ3:EZ20 FB3:FB20 FD3:FD20 FF3:FF20 FH3:FH20 FJ3:FJ20 FL3:FL20 FN3:FN20 FP3:FP20 FR3:FR20 FT3:FT20 FV3:FV20 FX3:FX20 FZ3:FZ20 GB3:GB20 GD3:GD20 GF3:GF20 GH3:GH20 GJ3:GJ20 GL3:GL20 GN3:GN20 GP3:GP20 GR3:GR20 GT3:GT20 GV3:GV20 GX3:GX20 GZ3:GZ20 HB3:HB20 HD3:HD20 HF3:HF20 HH3:HH20 HJ3:HJ20 HL3:HL20 HN3:HN20 HP3:HP20 HR3:HR20 HT3:HT20 HV3:HV20 HX3:HX20 HZ3:HZ20 IB3:IB20 ID3:ID20 IF3:IF20 IH3:IH20 IJ3:IJ20 IL3:IL20 IN3:IN20 IP3:IP20 IR3:IR20 IT3:IT20 IV3:IV20 IX3:IX20 IZ3:IZ20 JB3:JB20 JD3:JD20 JF3:JF20 JH3:JH20 JJ3:JJ20 JL3:JL20 JN3:JN20 JP3:JP20 JR3:JR20 JT3:JT20 JV3:JV20 JX3:JX20 JZ3:JZ20 KB3:KB20 KD3:KD20 KF3:KF20 KH3:KH20 KJ3:KJ20 KL3:KL20 KN3:KN20 KP3:KP20 KR3:KR20 KT3:KT20 KV3:KV20 KX3:KX20 KZ3:KZ20 LB3:LB20 LD3:LD20 LF3:LF20 LH3:LH20">
+      <formula1>数据!$A$1:$A$29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3 E3 G3 I3 K3 M3 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DC3 DE3 DG3 DI3 DK3 DM3 DO3 DQ3 DS3 DU3 DW3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 C4 E4 G4 I4 K4 M4 O4 Q4 S4 U4 W4 Y4 AA4 AC4 AE4 AG4 AI4 AK4 AM4 AO4 AQ4 AS4 AU4 AW4 AY4 BA4 BC4 BE4 BG4 BI4 BK4 BM4 BO4 BQ4 BS4 BU4 BW4 BY4 CA4 CC4 CE4 CG4 CI4 CK4 CM4 CO4 CQ4 CS4 CU4 CW4 CY4 DA4 DC4 DE4 DG4 DI4 DK4 DM4 DO4 DQ4 DS4 DU4 DW4 DY4 EA4 EC4 EE4 EG4 EI4 EK4 EM4 EO4 EQ4 ES4 EU4 EW4 EY4 FA4 FC4 FE4 FG4 FI4 FK4 FM4 FO4 FQ4 FS4 FU4 FW4 FY4 GA4 GC4 GE4 GG4 GI4 GK4 GM4 GO4 GQ4 GS4 GU4 GW4 GY4 HA4 HC4 HE4 HG4 HI4 HK4 HM4 HO4 HQ4 HS4 HU4 HW4 HY4 IA4 IC4 IE4 IG4 II4 IK4 IM4 IO4 IQ4 IS4 IU4 IW4 IY4 JA4 JC4 JE4 JG4 JI4 JK4 JM4 JO4 JQ4 JS4 JU4 JW4 JY4 KA4 KC4 KE4 KG4 KI4 KK4 KM4 KO4 KQ4 KS4 KU4 KW4 KY4 LA4 LC4 LE4 LG4 LI4 C5 E5 G5 I5 K5 M5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DC5 DE5 DG5 DI5 DK5 DM5 DO5 DQ5 DS5 DU5 DW5 DY5 EA5 EC5 EE5 EG5 EI5 EK5 EM5 EO5 EQ5 ES5 EU5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 KI5 KK5 KM5 KO5 KQ5 KS5 KU5 KW5 KY5 LA5 LC5 LE5 LG5 LI5 C6 E6 G6 I6 K6 M6 O6 Q6 S6 U6 W6 Y6 AA6 AC6 AE6 AG6 AI6 AK6 AM6 AO6 AQ6 AS6 AU6 AW6 AY6 BA6 BC6 BE6 BG6 BI6 BK6 BM6 BO6 BQ6 BS6 BU6 BW6 BY6 CA6 CC6 CE6 CG6 CI6 CK6 CM6 CO6 CQ6 CS6 CU6 CW6 CY6 DA6 DC6 DE6 DG6 DI6 DK6 DM6 DO6 DQ6 DS6 DU6 DW6 DY6 EA6 EC6 EE6 EG6 EI6 EK6 EM6 EO6 EQ6 ES6 EU6 EW6 EY6 FA6 FC6 FE6 FG6 FI6 FK6 FM6 FO6 FQ6 FS6 FU6 FW6 FY6 GA6 GC6 GE6 GG6 GI6 GK6 GM6 GO6 GQ6 GS6 GU6 GW6 GY6 HA6 HC6 HE6 HG6 HI6 HK6 HM6 HO6 HQ6 HS6 HU6 HW6 HY6 IA6 IC6 IE6 IG6 II6 IK6 IM6 IO6 IQ6 IS6 IU6 IW6 IY6 JA6 JC6 JE6 JG6 JI6 JK6 JM6 JO6 JQ6 JS6 JU6 JW6 JY6 KA6 KC6 KE6 KG6 KI6 KK6 KM6 KO6 KQ6 KS6 KU6 KW6 KY6 LA6 LC6 LE6 LG6 LI6 C7 E7 G7 I7 K7 M7 O7 Q7 S7 U7 W7 Y7 AA7 AC7 AE7 AG7 AI7 AK7 AM7 AO7 AQ7 AS7 AU7 AW7 AY7 BA7 BC7 BE7 BG7 BI7 BK7 BM7 BO7 BQ7 BS7 BU7 BW7 BY7 CA7 CC7 CE7 CG7 CI7 CK7 CM7 CO7 CQ7 CS7 CU7 CW7 CY7 DA7 DC7 DE7 DG7 DI7 DK7 DM7 DO7 DQ7 DS7 DU7 DW7 DY7 EA7 EC7 EE7 EG7 EI7 EK7 EM7 EO7 EQ7 ES7 EU7 EW7 EY7 FA7 FC7 FE7 FG7 FI7 FK7 FM7 FO7 FQ7 FS7 FU7 FW7 FY7 GA7 GC7 GE7 GG7 GI7 GK7 GM7 GO7 GQ7 GS7 GU7 GW7 GY7 HA7 HC7 HE7 HG7 HI7 HK7 HM7 HO7 HQ7 HS7 HU7 HW7 HY7 IA7 IC7 IE7 IG7 II7 IK7 IM7 IO7 IQ7 IS7 IU7 IW7 IY7 JA7 JC7 JE7 JG7 JI7 JK7 JM7 JO7 JQ7 JS7 JU7 JW7 JY7 KA7 KC7 KE7 KG7 KI7 KK7 KM7 KO7 KQ7 KS7 KU7 KW7 KY7 LA7 LC7 LE7 LG7 LI7 C8 E8 G8 I8 K8 M8 O8 Q8 S8 U8 W8 Y8 AA8 AC8 AE8 AG8 AI8 AK8 AM8 AO8 AQ8 AS8 AU8 AW8 AY8 BA8 BC8 BE8 BG8 BI8 BK8 BM8 BO8 BQ8 BS8 BU8 BW8 BY8 CA8 CC8 CE8 CG8 CI8 CK8 CM8 CO8 CQ8 CS8 CU8 CW8 CY8 DA8 DC8 DE8 DG8 DI8 DK8 DM8 DO8 DQ8 DS8 DU8 DW8 DY8 EA8 EC8 EE8 EG8 EI8 EK8 EM8 EO8 EQ8 ES8 EU8 EW8 EY8 FA8 FC8 FE8 FG8 FI8 FK8 FM8 FO8 FQ8 FS8 FU8 FW8 FY8 GA8 GC8 GE8 GG8 GI8 GK8 GM8 GO8 GQ8 GS8 GU8 GW8 GY8 HA8 HC8 HE8 HG8 HI8 HK8 HM8 HO8 HQ8 HS8 HU8 HW8 HY8 IA8 IC8 IE8 IG8 II8 IK8 IM8 IO8 IQ8 IS8 IU8 IW8 IY8 JA8 JC8 JE8 JG8 JI8 JK8 JM8 JO8 JQ8 JS8 JU8 JW8 JY8 KA8 KC8 KE8 KG8 KI8 KK8 KM8 KO8 KQ8 KS8 KU8 KW8 KY8 LA8 LC8 LE8 LG8 LI8 C9 E9 G9 I9 K9 M9 O9 Q9 S9 U9 W9 Y9 AA9 AC9 AE9 AG9 AI9 AK9 AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BW9 BY9 CA9 CC9 CE9 CG9 CI9 CK9 CM9 CO9 CQ9 CS9 CU9 CW9 CY9 DA9 DC9 DE9 DG9 DI9 DK9 DM9 DO9 DQ9 DS9 DU9 DW9 DY9 EA9 EC9 EE9 EG9 EI9 EK9 EM9 EO9 EQ9 ES9 EU9 EW9 EY9 FA9 FC9 FE9 FG9 FI9 FK9 FM9 FO9 FQ9 FS9 FU9 FW9 FY9 GA9 GC9 GE9 GG9 GI9 GK9 GM9 GO9 GQ9 GS9 GU9 GW9 GY9 HA9 HC9 HE9 HG9 HI9 HK9 HM9 HO9 HQ9 HS9 HU9 HW9 HY9 IA9 IC9 IE9 IG9 II9 IK9 IM9 IO9 IQ9 IS9 IU9 IW9 IY9 JA9 JC9 JE9 JG9 JI9 JK9 JM9 JO9 JQ9 JS9 JU9 JW9 JY9 KA9 KC9 KE9 KG9 KI9 KK9 KM9 KO9 KQ9 KS9 KU9 KW9 KY9 LA9 LC9 LE9 LG9 LI9 C10 E10 G10 I10 K10 M10 O10 Q10 S10 U10 W10 Y10 AA10 AC10 AE10 AG10 AI10 AK10 AM10 AO10 AQ10 AS10 AU10 AW10 AY10 BA10 BC10 BE10 BG10 BI10 BK10 BM10 BO10 BQ10 BS10 BU10 BW10 BY10 CA10 CC10 CE10 CG10 CI10 CK10 CM10 CO10 CQ10 CS10 CU10 CW10 CY10 DA10 DC10 DE10 DG10 DI10 DK10 DM10 DO10 DQ10 DS10 DU10 DW10 DY10 EA10 EC10 EE10 EG10 EI10 EK10 EM10 EO10 EQ10 ES10 EU10 EW10 EY10 FA10 FC10 FE10 FG10 FI10 FK10 FM10 FO10 FQ10 FS10 FU10 FW10 FY10 GA10 GC10 GE10 GG10 GI10 GK10 GM10 GO10 GQ10 GS10 GU10 GW10 GY10 HA10 HC10 HE10 HG10 HI10 HK10 HM10 HO10 HQ10 HS10 HU10 HW10 HY10 IA10 IC10 IE10 IG10 II10 IK10 IM10 IO10 IQ10 IS10 IU10 IW10 IY10 JA10 JC10 JE10 JG10 JI10 JK10 JM10 JO10 JQ10 JS10 JU10 JW10 JY10 KA10 KC10 KE10 KG10 KI10 KK10 KM10 KO10 KQ10 KS10 KU10 KW10 KY10 LA10 LC10 LE10 LG10 LI10 C11 E11 G11 I11 K11 M11 O11 Q11 S11 U11 W11 Y11 AA11 AC11 AE11 AG11 AI11 AK11 AM11 AO11 AQ11 AS11 AU11 AW11 AY11 BA11 BC11 BE11 BG11 BI11 BK11 BM11 BO11 BQ11 BS11 BU11 BW11 BY11 CA11 CC11 CE11 CG11 CI11 CK11 CM11 CO11 CQ11 CS11 CU11 CW11 CY11 DA11 DC11 DE11 DG11 DI11 DK11 DM11 DO11 DQ11 DS11 DU11 DW11 DY11 EA11 EC11 EE11 EG11 EI11 EK11 EM11 EO11 EQ11 ES11 EU11 EW11 EY11 FA11 FC11 FE11 FG11 FI11 FK11 FM11 FO11 FQ11 FS11 FU11 FW11 FY11 GA11 GC11 GE11 GG11 GI11 GK11 GM11 GO11 GQ11 GS11 GU11 GW11 GY11 HA11 HC11 HE11 HG11 HI11 HK11 HM11 HO11 HQ11 HS11 HU11 HW11 HY11 IA11 IC11 IE11 IG11 II11 IK11 IM11 IO11 IQ11 IS11 IU11 IW11 IY11 JA11 JC11 JE11 JG11 JI11 JK11 JM11 JO11 JQ11 JS11 JU11 JW11 JY11 KA11 KC11 KE11 KG11 KI11 KK11 KM11 KO11 KQ11 KS11 KU11 KW11 KY11 LA11 LC11 LE11 LG11 LI11 C12 E12 G12 I12 K12 M12 O12 Q12 S12 U12 W12 Y12 AA12 AC12 AE12 AG12 AI12 AK12 AM12 AO12 AQ12 AS12 AU12 AW12 AY12 BA12 BC12 BE12 BG12 BI12 BK12 BM12 BO12 BQ12 BS12 BU12 BW12 BY12 CA12 CC12 CE12 CG12 CI12 CK12 CM12 CO12 CQ12 CS12 CU12 CW12 CY12 DA12 DC12 DE12 DG12 DI12 DK12 DM12 DO12 DQ12 DS12 DU12 DW12 DY12 EA12 EC12 EE12 EG12 EI12 EK12 EM12 EO12 EQ12 ES12 EU12 EW12 EY12 FA12 FC12 FE12 FG12 FI12 FK12 FM12 FO12 FQ12 FS12 FU12 FW12 FY12 GA12 GC12 GE12 GG12 GI12 GK12 GM12 GO12 GQ12 GS12 GU12 GW12 GY12 HA12 HC12 HE12 HG12 HI12 HK12 HM12 HO12 HQ12 HS12 HU12 HW12 HY12 IA12 IC12 IE12 IG12 II12 IK12 IM12 IO12 IQ12 IS12 IU12 IW12 IY12 JA12 JC12 JE12 JG12 JI12 JK12 JM12 JO12 JQ12 JS12 JU12 JW12 JY12 KA12 KC12 KE12 KG12 KI12 KK12 KM12 KO12 KQ12 KS12 KU12 KW12 KY12 LA12 LC12 LE12 LG12 LI12 C13 E13 G13 I13 K13 M13 O13 Q13 S13 U13 W13 Y13 AA13 AC13 AE13 AG13 AI13 AK13 AM13 AO13 AQ13 AS13 AU13 AW13 AY13 BA13 BC13 BE13 BG13 BI13 BK13 BM13 BO13 BQ13 BS13 BU13 BW13 BY13 CA13 CC13 CE13 CG13 CI13 CK13 CM13 CO13 CQ13 CS13 CU13 CW13 CY13 DA13 DC13 DE13 DG13 DI13 DK13 DM13 DO13 DQ13 DS13 DU13 DW13 DY13 EA13 EC13 EE13 EG13 EI13 EK13 EM13 EO13 EQ13 ES13 EU13 EW13 EY13 FA13 FC13 FE13 FG13 FI13 FK13 FM13 FO13 FQ13 FS13 FU13 FW13 FY13 GA13 GC13 GE13 GG13 GI13 GK13 GM13 GO13 GQ13 GS13 GU13 GW13 GY13 HA13 HC13 HE13 HG13 HI13 HK13 HM13 HO13 HQ13 HS13 HU13 HW13 HY13 IA13 IC13 IE13 IG13 II13 IK13 IM13 IO13 IQ13 IS13 IU13 IW13 IY13 JA13 JC13 JE13 JG13 JI13 JK13 JM13 JO13 JQ13 JS13 JU13 JW13 JY13 KA13 KC13 KE13 KG13 KI13 KK13 KM13 KO13 KQ13 KS13 KU13 KW13 KY13 LA13 LC13 LE13 LG13 LI13 C14 E14 G14 I14 K14 M14 O14 Q14 S14 U14 W14 Y14 AA14 AC14 AE14 AG14 AI14 AK14 AM14 AO14 AQ14 AS14 AU14 AW14 AY14 BA14 BC14 BE14 BG14 BI14 BK14 BM14 BO14 BQ14 BS14 BU14 BW14 BY14 CA14 CC14 CE14 CG14 CI14 CK14 CM14 CO14 CQ14 CS14 CU14 CW14 CY14 DA14 DC14 DE14 DG14 DI14 DK14 DM14 DO14 DQ14 DS14 DU14 DW14 DY14 EA14 EC14 EE14 EG14 EI14 EK14 EM14 EO14 EQ14 ES14 EU14 EW14 EY14 FA14 FC14 FE14 FG14 FI14 FK14 FM14 FO14 FQ14 FS14 FU14 FW14 FY14 GA14 GC14 GE14 GG14 GI14 GK14 GM14 GO14 GQ14 GS14 GU14 GW14 GY14 HA14 HC14 HE14 HG14 HI14 HK14 HM14 HO14 HQ14 HS14 HU14 HW14 HY14 IA14 IC14 IE14 IG14 II14 IK14 IM14 IO14 IQ14 IS14 IU14 IW14 IY14 JA14 JC14 JE14 JG14 JI14 JK14 JM14 JO14 JQ14 JS14 JU14 JW14 JY14 KA14 KC14 KE14 KG14 KI14 KK14 KM14 KO14 KQ14 KS14 KU14 KW14 KY14 LA14 LC14 LE14 LG14 LI14 C15 E15 G15 I15 K15 M15 O15 Q15 S15 U15 W15 Y15 AA15 AC15 AE15 AG15 AI15 AK15 AM15 AO15 AQ15 AS15 AU15 AW15 AY15 BA15 BC15 BE15 BG15 BI15 BK15 BM15 BO15 BQ15 BS15 BU15 BW15 BY15 CA15 CC15 CE15 CG15 CI15 CK15 CM15 CO15 CQ15 CS15 CU15 CW15 CY15 DA15 DC15 DE15 DG15 DI15 DK15 DM15 DO15 DQ15 DS15 DU15 DW15 DY15 EA15 EC15 EE15 EG15 EI15 EK15 EM15 EO15 EQ15 ES15 EU15 EW15 EY15 FA15 FC15 FE15 FG15 FI15 FK15 FM15 FO15 FQ15 FS15 FU15 FW15 FY15 GA15 GC15 GE15 GG15 GI15 GK15 GM15 GO15 GQ15 GS15 GU15 GW15 GY15 HA15 HC15 HE15 HG15 HI15 HK15 HM15 HO15 HQ15 HS15 HU15 HW15 HY15 IA15 IC15 IE15 IG15 II15 IK15 IM15 IO15 IQ15 IS15 IU15 IW15 IY15 JA15 JC15 JE15 JG15 JI15 JK15 JM15 JO15 JQ15 JS15 JU15 JW15 JY15 KA15 KC15 KE15 KG15 KI15 KK15 KM15 KO15 KQ15 KS15 KU15 KW15 KY15 LA15 LC15 LE15 LG15 LI15 C16 E16 G16 I16 K16 M16 O16 Q16 S16 U16 W16 Y16 AA16 AC16 AE16 AG16 AI16 AK16 AM16 AO16 AQ16 AS16 AU16 AW16 AY16 BA16 BC16 BE16 BG16 BI16 BK16 BM16 BO16 BQ16 BS16 BU16 BW16 BY16 CA16 CC16 CE16 CG16 CI16 CK16 CM16 CO16 CQ16 CS16 CU16 CW16 CY16 DA16 DC16 DE16 DG16 DI16 DK16 DM16 DO16 DQ16 DS16 DU16 DW16 DY16 EA16 EC16 EE16 EG16 EI16 EK16 EM16 EO16 EQ16 ES16 EU16 EW16 EY16 FA16 FC16 FE16 FG16 FI16 FK16 FM16 FO16 FQ16 FS16 FU16 FW16 FY16 GA16 GC16 GE16 GG16 GI16 GK16 GM16 GO16 GQ16 GS16 GU16 GW16 GY16 HA16 HC16 HE16 HG16 HI16 HK16 HM16 HO16 HQ16 HS16 HU16 HW16 HY16 IA16 IC16 IE16 IG16 II16 IK16 IM16 IO16 IQ16 IS16 IU16 IW16 IY16 JA16 JC16 JE16 JG16 JI16 JK16 JM16 JO16 JQ16 JS16 JU16 JW16 JY16 KA16 KC16 KE16 KG16 KI16 KK16 KM16 KO16 KQ16 KS16 KU16 KW16 KY16 LA16 LC16 LE16 LG16 LI16 C17 E17 G17 I17 K17 M17 O17 Q17 S17 U17 W17 Y17 AA17 AC17 AE17 AG17 AI17 AK17 AM17 AO17 AQ17 AS17 AU17 AW17 AY17 BA17 BC17 BE17 BG17 BI17 BK17 BM17 BO17 BQ17 BS17 BU17 BW17 BY17 CA17 CC17 CE17 CG17 CI17 CK17 CM17 CO17 CQ17 CS17 CU17 CW17 CY17 DA17 DC17 DE17 DG17 DI17 DK17 DM17 DO17 DQ17 DS17 DU17 DW17 DY17 EA17 EC17 EE17 EG17 EI17 EK17 EM17 EO17 EQ17 ES17 EU17 EW17 EY17 FA17 FC17 FE17 FG17 FI17 FK17 FM17 FO17 FQ17 FS17 FU17 FW17 FY17 GA17 GC17 GE17 GG17 GI17 GK17 GM17 GO17 GQ17 GS17 GU17 GW17 GY17 HA17 HC17 HE17 HG17 HI17 HK17 HM17 HO17 HQ17 HS17 HU17 HW17 HY17 IA17 IC17 IE17 IG17 II17 IK17 IM17 IO17 IQ17 IS17 IU17 IW17 IY17 JA17 JC17 JE17 JG17 JI17 JK17 JM17 JO17 JQ17 JS17 JU17 JW17 JY17 KA17 KC17 KE17 KG17 KI17 KK17 KM17 KO17 KQ17 KS17 KU17 KW17 KY17 LA17 LC17 LE17 LG17 LI17 C18 E18 G18 I18 K18 M18 O18 Q18 S18 U18 W18 Y18 AA18 AC18 AE18 AG18 AI18 AK18 AM18 AO18 AQ18 AS18 AU18 AW18 AY18 BA18 BC18 BE18 BG18 BI18 BK18 BM18 BO18 BQ18 BS18 BU18 BW18 BY18 CA18 CC18 CE18 CG18 CI18 CK18 CM18 CO18 CQ18 CS18 CU18 CW18 CY18 DA18 DC18 DE18 DG18 DI18 DK18 DM18 DO18 DQ18 DS18 DU18 DW18 DY18 EA18 EC18 EE18 EG18 EI18 EK18 EM18 EO18 EQ18 ES18 EU18 EW18 EY18 FA18 FC18 FE18 FG18 FI18 FK18 FM18 FO18 FQ18 FS18 FU18 FW18 FY18 GA18 GC18 GE18 GG18 GI18 GK18 GM18 GO18 GQ18 GS18 GU18 GW18 GY18 HA18 HC18 HE18 HG18 HI18 HK18 HM18 HO18 HQ18 HS18 HU18 HW18 HY18 IA18 IC18 IE18 IG18 II18 IK18 IM18 IO18 IQ18 IS18 IU18 IW18 IY18 JA18 JC18 JE18 JG18 JI18 JK18 JM18 JO18 JQ18 JS18 JU18 JW18 JY18 KA18 KC18 KE18 KG18 KI18 KK18 KM18 KO18 KQ18 KS18 KU18 KW18 KY18 LA18 LC18 LE18 LG18 LI18 C19 E19 G19 I19 K19 M19 O19 Q19 S19 U19 W19 Y19 AA19 AC19 AE19 AG19 AI19 AK19 AM19 AO19 AQ19 AS19 AU19 AW19 AY19 BA19 BC19 BE19 BG19 BI19 BK19 BM19 BO19 BQ19 BS19 BU19 BW19 BY19 CA19 CC19 CE19 CG19 CI19 CK19 CM19 CO19 CQ19 CS19 CU19 CW19 CY19 DA19 DC19 DE19 DG19 DI19 DK19 DM19 DO19 DQ19 DS19 DU19 DW19 DY19 EA19 EC19 EE19 EG19 EI19 EK19 EM19 EO19 EQ19 ES19 EU19 EW19 EY19 FA19 FC19 FE19 FG19 FI19 FK19 FM19 FO19 FQ19 FS19 FU19 FW19 FY19 GA19 GC19 GE19 GG19 GI19 GK19 GM19 GO19 GQ19 GS19 GU19 GW19 GY19 HA19 HC19 HE19 HG19 HI19 HK19 HM19 HO19 HQ19 HS19 HU19 HW19 HY19 IA19 IC19 IE19 IG19 II19 IK19 IM19 IO19 IQ19 IS19 IU19 IW19 IY19 JA19 JC19 JE19 JG19 JI19 JK19 JM19 JO19 JQ19 JS19 JU19 JW19 JY19 KA19 KC19 KE19 KG19 KI19 KK19 KM19 KO19 KQ19 KS19 KU19 KW19 KY19 LA19 LC19 LE19 LG19 LI19 C20 E20 G20 I20 K20 M20 O20 Q20 S20 U20 W20 Y20 AA20 AC20 AE20 AG20 AI20 AK20 AM20 AO20 AQ20 AS20 AU20 AW20 AY20 BA20 BC20 BE20 BG20 BI20 BK20 BM20 BO20 BQ20 BS20 BU20 BW20 BY20 CA20 CC20 CE20 CG20 CI20 CK20 CM20 CO20 CQ20 CS20 CU20 CW20 CY20 DA20 DC20 DE20 DG20 DI20 DK20 DM20 DO20 DQ20 DS20 DU20 DW20 DY20 EA20 EC20 EE20 EG20 EI20 EK20 EM20 EO20 EQ20 ES20 EU20 EW20 EY20 FA20 FC20 FE20 FG20 FI20 FK20 FM20 FO20 FQ20 FS20 FU20 FW20 FY20 GA20 GC20 GE20 GG20 GI20 GK20 GM20 GO20 GQ20 GS20 GU20 GW20 GY20 HA20 HC20 HE20 HG20 HI20 HK20 HM20 HO20 HQ20 HS20 HU20 HW20 HY20 IA20 IC20 IE20 IG20 II20 IK20 IM20 IO20 IQ20 IS20 IU20 IW20 IY20 JA20 JC20 JE20 JG20 JI20 JK20 JM20 JO20 JQ20 JS20 JU20 JW20 JY20 KA20 KC20 KE20 KG20 KI20 KK20 KM20 KO20 KQ20 KS20 KU20 KW20 KY20 LA20 LC20 LE20 LG20 LI20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3 E3 G3 C4 E4 G4 C5 E5 G5 C6 E6 G6 C7 E7 G7 C8 E8 G8 C9 E9 G9 C10 E10 G10 C11 E11 G11 C12 E12 G12 C13 E13 G13 C14 E14 G14 C15 E15 G15 C16 E16 G16 C17 E17 G17 C18 E18 G18 C19 E19 G19 C20 E20 G20 I20 K20 M20 I3:I19 K3:K19 M3:M19 O3:O20 Q3:Q20 S3:S20 U3:U20 W3:W20 Y3:Y20 AA3:AA20 AC3:AC20 AE3:AE20 AG3:AG20 AI3:AI20 AK3:AK20 AM3:AM20 AO3:AO20 AQ3:AQ20 AS3:AS20 AU3:AU20 AW3:AW20 AY3:AY20 BA3:BA20 BC3:BC20 BE3:BE20 BG3:BG20 BI3:BI20 BK3:BK20 BM3:BM20 BO3:BO20 BQ3:BQ20 BS3:BS20 BU3:BU20 BW3:BW20 BY3:BY20 CA3:CA20 CC3:CC20 CE3:CE20 CG3:CG20 CI3:CI20 CK3:CK20 CM3:CM20 CO3:CO20 CQ3:CQ20 CS3:CS20 CU3:CU20 CW3:CW20 CY3:CY20 DA3:DA20 DC3:DC20 DE3:DE20 DG3:DG20 DI3:DI20 DK3:DK20 DM3:DM20 DO3:DO20 DQ3:DQ20 DS3:DS20 DU3:DU20 DW3:DW20 DY3:DY20 EA3:EA20 EC3:EC20 EE3:EE20 EG3:EG20 EI3:EI20 EK3:EK20 EM3:EM20 EO3:EO20 EQ3:EQ20 ES3:ES20 EU3:EU20 EW3:EW20 EY3:EY20 FA3:FA20 FC3:FC20 FE3:FE20 FG3:FG20 FI3:FI20 FK3:FK20 FM3:FM20 FO3:FO20 FQ3:FQ20 FS3:FS20 FU3:FU20 FW3:FW20 FY3:FY20 GA3:GA20 GC3:GC20 GE3:GE20 GG3:GG20 GI3:GI20 GK3:GK20 GM3:GM20 GO3:GO20 GQ3:GQ20 GS3:GS20 GU3:GU20 GW3:GW20 GY3:GY20 HA3:HA20 HC3:HC20 HE3:HE20 HG3:HG20 HI3:HI20 HK3:HK20 HM3:HM20 HO3:HO20 HQ3:HQ20 HS3:HS20 HU3:HU20 HW3:HW20 HY3:HY20 IA3:IA20 IC3:IC20 IE3:IE20 IG3:IG20 II3:II20 IK3:IK20 IM3:IM20 IO3:IO20 IQ3:IQ20 IS3:IS20 IU3:IU20 IW3:IW20 IY3:IY20 JA3:JA20 JC3:JC20 JE3:JE20 JG3:JG20 JI3:JI20 JK3:JK20 JM3:JM20 JO3:JO20 JQ3:JQ20 JS3:JS20 JU3:JU20 JW3:JW20 JY3:JY20 KA3:KA20 KC3:KC20 KE3:KE20 KG3:KG20 KI3:KI20 KK3:KK20 KM3:KM20 KO3:KO20 KQ3:KQ20 KS3:KS20 KU3:KU20 KW3:KW20 KY3:KY20 LA3:LA20 LC3:LC20 LE3:LE20 LG3:LG20 LI3:LI20">
       <formula1>数据!$B$1:$B$55</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C21 E21 G21 I21 K21 M21 O21 Q21 S21 U21 W21 Y21 AA21 AC21 AE21 AG21 AI21 AK21 AM21 AO21 AQ21 AS21 AU21 AW21 AY21 BA21 BC21 BE21 BG21 BI21 BK21 BM21 BO21 BQ21 BS21 BU21 BW21 BY21 CA21 CC21 CE21 CG21 CI21 CK21 CM21 CO21 CQ21 CS21 CU21 CW21 CY21 DA21 DC21 DE21 DG21 DI21 DK21 DM21 DO21 DQ21 DS21 DU21 DW21 DY21 EA21 EC21 EE21 EG21 EI21 EK21 EM21 EO21 EQ21 ES21 EU21 EW21 EY21 FA21 FC21 FE21 FG21 FI21 FK21 FM21 FO21 FQ21 FS21 FU21 FW21 FY21 GA21 GC21 GE21 GG21 GI21 GK21 GM21 GO21 GQ21 GS21 GU21 GW21 GY21 HA21 HC21 HE21 HG21 HI21 HK21 HM21 HO21 HQ21 HS21 HU21 HW21 HY21 IA21 IC21 IE21 IG21 II21 IK21 IM21 IO21 IQ21 IS21 IU21 IW21 IY21 JA21 JC21 JE21 JG21 JI21 JK21 JM21 JO21 JQ21 JS21 JU21 JW21 JY21 KA21 KC21 KE21 KG21 KI21 KK21 KM21 KO21 KQ21 KS21 KU21 KW21 KY21 LA21 LC21 LE21 LG21 LI21">
@@ -9522,7 +9561,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0.75</v>
@@ -9533,7 +9572,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -9555,7 +9594,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>1.5</v>
@@ -9577,7 +9616,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -9588,7 +9627,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>2.25</v>
@@ -9599,7 +9638,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>2.5</v>
@@ -9610,7 +9649,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>2.75</v>
@@ -9642,7 +9681,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15">
@@ -9665,7 +9704,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -9676,7 +9715,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B18">
         <v>4.25</v>
@@ -9786,7 +9825,10 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="29" spans="2:2">
+    <row r="29" spans="1:2">
+      <c r="A29" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="B29">
         <v>7</v>
       </c>
@@ -9939,22 +9981,22 @@
     <row r="1" ht="15" spans="1:7">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:7">
@@ -9992,7 +10034,7 @@
     </row>
     <row r="5" ht="15" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="1"/>
@@ -10003,7 +10045,7 @@
     </row>
     <row r="6" ht="15" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="1"/>
@@ -10025,7 +10067,7 @@
     </row>
     <row r="8" ht="15" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="1"/>
@@ -10047,7 +10089,7 @@
     </row>
     <row r="10" ht="15" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="1"/>
@@ -10058,7 +10100,7 @@
     </row>
     <row r="11" ht="15" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -10069,7 +10111,7 @@
     </row>
     <row r="12" ht="15" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>

--- a/c/拖课统计.xlsx
+++ b/c/拖课统计.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="98">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -49,7 +49,7 @@
     <t>语文</t>
   </si>
   <si>
-    <t>英语（占）</t>
+    <t>音乐（英占）</t>
   </si>
   <si>
     <t>体育</t>
@@ -76,6 +76,9 @@
     <t>劳技</t>
   </si>
   <si>
+    <t>音乐（数、英占½）</t>
+  </si>
+  <si>
     <t>地理</t>
   </si>
   <si>
@@ -97,43 +100,211 @@
     <t>其他</t>
   </si>
   <si>
-    <t>语文（占）</t>
+    <t>音乐（语占）</t>
   </si>
   <si>
-    <t>数学（占）</t>
+    <t>体育（语占）</t>
   </si>
   <si>
-    <t>政治（占）</t>
+    <t>美术（语占）</t>
   </si>
   <si>
-    <t>历史（占）</t>
+    <t>劳技（语占）</t>
   </si>
   <si>
-    <t>地理（占）</t>
+    <t>信息（语占）</t>
   </si>
   <si>
-    <t>生物（占）</t>
+    <t>音乐（数占）</t>
   </si>
   <si>
-    <t>语文（占½）</t>
+    <t>体育（数占）</t>
   </si>
   <si>
-    <t>数学（占½）</t>
+    <t>美术（数占）</t>
   </si>
   <si>
-    <t>英语（占½）</t>
+    <t>劳技（数占）</t>
   </si>
   <si>
-    <t>政治（占½）</t>
+    <t>信息（数占）</t>
   </si>
   <si>
-    <t>历史（占½）</t>
+    <t>体育（英占）</t>
   </si>
   <si>
-    <t>地理（占½）</t>
+    <t>美术（英占）</t>
   </si>
   <si>
-    <t>生物（占½）</t>
+    <t>劳技（英占）</t>
+  </si>
+  <si>
+    <t>信息（英占）</t>
+  </si>
+  <si>
+    <t>音乐（政占）</t>
+  </si>
+  <si>
+    <t>体育（政占）</t>
+  </si>
+  <si>
+    <t>美术（政占）</t>
+  </si>
+  <si>
+    <t>劳技（政占）</t>
+  </si>
+  <si>
+    <t>信息（政占）</t>
+  </si>
+  <si>
+    <t>音乐（史占）</t>
+  </si>
+  <si>
+    <t>体育（史占）</t>
+  </si>
+  <si>
+    <t>美术（史占）</t>
+  </si>
+  <si>
+    <t>劳技（史占）</t>
+  </si>
+  <si>
+    <t>信息（史占）</t>
+  </si>
+  <si>
+    <t>音乐（地占）</t>
+  </si>
+  <si>
+    <t>体育（地占）</t>
+  </si>
+  <si>
+    <t>美术（地占）</t>
+  </si>
+  <si>
+    <t>劳技（地占）</t>
+  </si>
+  <si>
+    <t>信息（地占）</t>
+  </si>
+  <si>
+    <t>音乐（生占）</t>
+  </si>
+  <si>
+    <t>体育（生占）</t>
+  </si>
+  <si>
+    <t>美术（生占）</t>
+  </si>
+  <si>
+    <t>劳技（生占）</t>
+  </si>
+  <si>
+    <t>信息（生占）</t>
+  </si>
+  <si>
+    <t>音乐（语占½）</t>
+  </si>
+  <si>
+    <t>体育（语占½）</t>
+  </si>
+  <si>
+    <t>美术（语占½）</t>
+  </si>
+  <si>
+    <t>劳技（语占½）</t>
+  </si>
+  <si>
+    <t>信息（语占½）</t>
+  </si>
+  <si>
+    <t>音乐（数占½）</t>
+  </si>
+  <si>
+    <t>体育（数占½）</t>
+  </si>
+  <si>
+    <t>美术（数占½）</t>
+  </si>
+  <si>
+    <t>劳技（数占½）</t>
+  </si>
+  <si>
+    <t>信息（数占½）</t>
+  </si>
+  <si>
+    <t>音乐（英占½）</t>
+  </si>
+  <si>
+    <t>体育（英占½）</t>
+  </si>
+  <si>
+    <t>美术（英占½）</t>
+  </si>
+  <si>
+    <t>劳技（英占½）</t>
+  </si>
+  <si>
+    <t>信息（英占½）</t>
+  </si>
+  <si>
+    <t>音乐（政占½）</t>
+  </si>
+  <si>
+    <t>体育（政占½）</t>
+  </si>
+  <si>
+    <t>美术（政占½）</t>
+  </si>
+  <si>
+    <t>劳技（政占½）</t>
+  </si>
+  <si>
+    <t>信息（政占½）</t>
+  </si>
+  <si>
+    <t>音乐（史占½）</t>
+  </si>
+  <si>
+    <t>体育（史占½）</t>
+  </si>
+  <si>
+    <t>美术（史占½）</t>
+  </si>
+  <si>
+    <t>劳技（史占½）</t>
+  </si>
+  <si>
+    <t>信息（史占½）</t>
+  </si>
+  <si>
+    <t>音乐（地占½）</t>
+  </si>
+  <si>
+    <t>体育（地占½）</t>
+  </si>
+  <si>
+    <t>美术（地占½）</t>
+  </si>
+  <si>
+    <t>劳技（地占½）</t>
+  </si>
+  <si>
+    <t>信息（地占½）</t>
+  </si>
+  <si>
+    <t>音乐（生占½）</t>
+  </si>
+  <si>
+    <t>体育（生占½）</t>
+  </si>
+  <si>
+    <t>美术（生占½）</t>
+  </si>
+  <si>
+    <t>劳技（生占½）</t>
+  </si>
+  <si>
+    <t>信息（生占½）</t>
   </si>
   <si>
     <t>语文+英语</t>
@@ -167,7 +338,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -183,12 +354,6 @@
       <sz val="12"/>
       <color rgb="FFD9E1F4"/>
       <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -366,7 +531,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -430,6 +595,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -844,28 +1015,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -874,118 +1048,115 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1002,28 +1173,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1032,52 +1203,52 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1132,7 +1303,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1157,14 +1328,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.8"/>
+          <bgColor rgb="FFFCE4D3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2778,10 +2942,18 @@
       <c r="S3" s="16"/>
       <c r="T3" s="15"/>
       <c r="U3" s="16"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="16"/>
-      <c r="X3" s="15"/>
-      <c r="Y3" s="16"/>
+      <c r="V3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="W3" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="X3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="16" t="s">
+        <v>3</v>
+      </c>
       <c r="Z3" s="15"/>
       <c r="AA3" s="16"/>
       <c r="AB3" s="15"/>
@@ -3450,10 +3622,18 @@
       <c r="S5" s="22"/>
       <c r="T5" s="21"/>
       <c r="U5" s="22"/>
-      <c r="V5" s="21"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="21"/>
-      <c r="Y5" s="22"/>
+      <c r="V5" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="W5" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="X5" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="22">
+        <v>1.75</v>
+      </c>
       <c r="Z5" s="21"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="21"/>
@@ -4122,10 +4302,18 @@
       <c r="S7" s="22"/>
       <c r="T7" s="23"/>
       <c r="U7" s="22"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="23"/>
-      <c r="Y7" s="22"/>
+      <c r="V7" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="W7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="16" t="s">
+        <v>3</v>
+      </c>
       <c r="Z7" s="23"/>
       <c r="AA7" s="22"/>
       <c r="AB7" s="23"/>
@@ -4798,10 +4986,18 @@
       <c r="S9" s="22"/>
       <c r="T9" s="21"/>
       <c r="U9" s="22"/>
-      <c r="V9" s="21"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="22"/>
+      <c r="V9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y9" s="16" t="s">
+        <v>3</v>
+      </c>
       <c r="Z9" s="21"/>
       <c r="AA9" s="22"/>
       <c r="AB9" s="21"/>
@@ -5466,10 +5662,18 @@
       <c r="S11" s="22"/>
       <c r="T11" s="21"/>
       <c r="U11" s="22"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="22"/>
+      <c r="V11" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="W11" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="X11" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="16" t="s">
+        <v>3</v>
+      </c>
       <c r="Z11" s="21"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="21"/>
@@ -6134,10 +6338,18 @@
       <c r="S13" s="22"/>
       <c r="T13" s="21"/>
       <c r="U13" s="22"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="22"/>
+      <c r="V13" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="W13" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="X13" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y13" s="22">
+        <v>1</v>
+      </c>
       <c r="Z13" s="21"/>
       <c r="AA13" s="22"/>
       <c r="AB13" s="21"/>
@@ -6781,7 +6993,7 @@
         <v>3</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M15" s="22">
         <v>2</v>
@@ -6793,7 +7005,7 @@
         <v>3</v>
       </c>
       <c r="P15" s="21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q15" s="22">
         <v>1.25</v>
@@ -6802,10 +7014,18 @@
       <c r="S15" s="22"/>
       <c r="T15" s="21"/>
       <c r="U15" s="22"/>
-      <c r="V15" s="21"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="22"/>
+      <c r="V15" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="W15" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="X15" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y15" s="16" t="s">
+        <v>3</v>
+      </c>
       <c r="Z15" s="21"/>
       <c r="AA15" s="22"/>
       <c r="AB15" s="21"/>
@@ -7470,10 +7690,18 @@
       <c r="S17" s="22"/>
       <c r="T17" s="21"/>
       <c r="U17" s="22"/>
-      <c r="V17" s="21"/>
-      <c r="W17" s="22"/>
-      <c r="X17" s="21"/>
-      <c r="Y17" s="22"/>
+      <c r="V17" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="W17" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y17" s="22">
+        <v>3</v>
+      </c>
       <c r="Z17" s="21"/>
       <c r="AA17" s="22"/>
       <c r="AB17" s="21"/>
@@ -8129,7 +8357,7 @@
         <v>3</v>
       </c>
       <c r="P19" s="21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q19" s="22" t="s">
         <v>3</v>
@@ -8138,10 +8366,18 @@
       <c r="S19" s="22"/>
       <c r="T19" s="21"/>
       <c r="U19" s="22"/>
-      <c r="V19" s="21"/>
-      <c r="W19" s="22"/>
-      <c r="X19" s="21"/>
-      <c r="Y19" s="22"/>
+      <c r="V19" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="W19" s="22">
+        <v>0.25</v>
+      </c>
+      <c r="X19" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y19" s="16" t="s">
+        <v>3</v>
+      </c>
       <c r="Z19" s="21"/>
       <c r="AA19" s="22"/>
       <c r="AB19" s="21"/>
@@ -8765,643 +9001,643 @@
     <row r="21" ht="17.5" spans="1:321">
       <c r="A21" s="27"/>
       <c r="B21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" s="29"/>
       <c r="F21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" s="29"/>
       <c r="H21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" s="29"/>
       <c r="J21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K21" s="29"/>
       <c r="L21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M21" s="29"/>
       <c r="N21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O21" s="29"/>
       <c r="P21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q21" s="29"/>
       <c r="R21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S21" s="29"/>
       <c r="T21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U21" s="29"/>
       <c r="V21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W21" s="29"/>
       <c r="X21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y21" s="29"/>
       <c r="Z21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA21" s="29"/>
       <c r="AB21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC21" s="29"/>
       <c r="AD21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE21" s="29"/>
       <c r="AF21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG21" s="29"/>
       <c r="AH21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI21" s="29"/>
       <c r="AJ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK21" s="29"/>
       <c r="AL21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM21" s="29"/>
       <c r="AN21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO21" s="29"/>
       <c r="AP21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ21" s="29"/>
       <c r="AR21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS21" s="29"/>
       <c r="AT21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU21" s="29"/>
       <c r="AV21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW21" s="29"/>
       <c r="AX21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY21" s="29"/>
       <c r="AZ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA21" s="29"/>
       <c r="BB21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC21" s="29"/>
       <c r="BD21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BE21" s="29"/>
       <c r="BF21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG21" s="29"/>
       <c r="BH21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BI21" s="29"/>
       <c r="BJ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BK21" s="29"/>
       <c r="BL21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BM21" s="29"/>
       <c r="BN21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BO21" s="29"/>
       <c r="BP21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BQ21" s="29"/>
       <c r="BR21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BS21" s="29"/>
       <c r="BT21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BU21" s="29"/>
       <c r="BV21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW21" s="29"/>
       <c r="BX21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BY21" s="29"/>
       <c r="BZ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CA21" s="29"/>
       <c r="CB21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CC21" s="29"/>
       <c r="CD21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CE21" s="29"/>
       <c r="CF21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CG21" s="29"/>
       <c r="CH21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CI21" s="29"/>
       <c r="CJ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CK21" s="29"/>
       <c r="CL21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CM21" s="29"/>
       <c r="CN21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CO21" s="29"/>
       <c r="CP21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CQ21" s="29"/>
       <c r="CR21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CS21" s="29"/>
       <c r="CT21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CU21" s="29"/>
       <c r="CV21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CW21" s="29"/>
       <c r="CX21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CY21" s="29"/>
       <c r="CZ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DA21" s="29"/>
       <c r="DB21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DC21" s="29"/>
       <c r="DD21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DE21" s="29"/>
       <c r="DF21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DG21" s="29"/>
       <c r="DH21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DI21" s="29"/>
       <c r="DJ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DK21" s="29"/>
       <c r="DL21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DM21" s="29"/>
       <c r="DN21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DO21" s="29"/>
       <c r="DP21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DQ21" s="29"/>
       <c r="DR21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DS21" s="29"/>
       <c r="DT21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DU21" s="29"/>
       <c r="DV21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DW21" s="29"/>
       <c r="DX21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DY21" s="29"/>
       <c r="DZ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EA21" s="29"/>
       <c r="EB21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EC21" s="29"/>
       <c r="ED21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EE21" s="29"/>
       <c r="EF21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EG21" s="29"/>
       <c r="EH21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EI21" s="29"/>
       <c r="EJ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EK21" s="29"/>
       <c r="EL21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EM21" s="29"/>
       <c r="EN21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EO21" s="29"/>
       <c r="EP21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EQ21" s="29"/>
       <c r="ER21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="ES21" s="29"/>
       <c r="ET21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EU21" s="29"/>
       <c r="EV21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EW21" s="29"/>
       <c r="EX21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EY21" s="29"/>
       <c r="EZ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FA21" s="29"/>
       <c r="FB21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FC21" s="29"/>
       <c r="FD21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FE21" s="29"/>
       <c r="FF21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FG21" s="29"/>
       <c r="FH21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FI21" s="29"/>
       <c r="FJ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FK21" s="29"/>
       <c r="FL21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FM21" s="29"/>
       <c r="FN21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FO21" s="29"/>
       <c r="FP21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FQ21" s="29"/>
       <c r="FR21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FS21" s="29"/>
       <c r="FT21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FU21" s="29"/>
       <c r="FV21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FW21" s="29"/>
       <c r="FX21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="FY21" s="29"/>
       <c r="FZ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GA21" s="29"/>
       <c r="GB21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GC21" s="29"/>
       <c r="GD21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GE21" s="29"/>
       <c r="GF21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GG21" s="29"/>
       <c r="GH21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GI21" s="29"/>
       <c r="GJ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GK21" s="29"/>
       <c r="GL21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GM21" s="29"/>
       <c r="GN21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GO21" s="29"/>
       <c r="GP21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GQ21" s="29"/>
       <c r="GR21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GS21" s="29"/>
       <c r="GT21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GU21" s="29"/>
       <c r="GV21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GW21" s="29"/>
       <c r="GX21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="GY21" s="29"/>
       <c r="GZ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HA21" s="29"/>
       <c r="HB21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HC21" s="29"/>
       <c r="HD21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HE21" s="29"/>
       <c r="HF21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HG21" s="29"/>
       <c r="HH21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HI21" s="29"/>
       <c r="HJ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HK21" s="29"/>
       <c r="HL21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HM21" s="29"/>
       <c r="HN21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HO21" s="29"/>
       <c r="HP21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HQ21" s="29"/>
       <c r="HR21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HS21" s="29"/>
       <c r="HT21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HU21" s="29"/>
       <c r="HV21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HW21" s="29"/>
       <c r="HX21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="HY21" s="29"/>
       <c r="HZ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="IA21" s="29"/>
       <c r="IB21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="IC21" s="29"/>
       <c r="ID21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="IE21" s="29"/>
       <c r="IF21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="IG21" s="29"/>
       <c r="IH21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="II21" s="29"/>
       <c r="IJ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="IK21" s="29"/>
       <c r="IL21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="IM21" s="29"/>
       <c r="IN21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="IO21" s="29"/>
       <c r="IP21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="IQ21" s="29"/>
       <c r="IR21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="IS21" s="29"/>
       <c r="IT21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="IU21" s="29"/>
       <c r="IV21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="IW21" s="29"/>
       <c r="IX21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="IY21" s="29"/>
       <c r="IZ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JA21" s="29"/>
       <c r="JB21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JC21" s="29"/>
       <c r="JD21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JE21" s="29"/>
       <c r="JF21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JG21" s="29"/>
       <c r="JH21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JI21" s="29"/>
       <c r="JJ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JK21" s="29"/>
       <c r="JL21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JM21" s="29"/>
       <c r="JN21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JO21" s="29"/>
       <c r="JP21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JQ21" s="29"/>
       <c r="JR21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JS21" s="29"/>
       <c r="JT21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JU21" s="29"/>
       <c r="JV21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JW21" s="29"/>
       <c r="JX21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="JY21" s="29"/>
       <c r="JZ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KA21" s="29"/>
       <c r="KB21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KC21" s="29"/>
       <c r="KD21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KE21" s="29"/>
       <c r="KF21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KG21" s="29"/>
       <c r="KH21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KI21" s="29"/>
       <c r="KJ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KK21" s="29"/>
       <c r="KL21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KM21" s="29"/>
       <c r="KN21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KO21" s="29"/>
       <c r="KP21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KQ21" s="29"/>
       <c r="KR21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KS21" s="29"/>
       <c r="KT21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KU21" s="29"/>
       <c r="KV21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KW21" s="29"/>
       <c r="KX21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="KY21" s="29"/>
       <c r="KZ21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="LA21" s="29"/>
       <c r="LB21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="LC21" s="29"/>
       <c r="LD21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="LE21" s="29"/>
       <c r="LF21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="LG21" s="29"/>
       <c r="LH21" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="LI21" s="29"/>
     </row>
@@ -9572,7 +9808,7 @@
     <mergeCell ref="LF2:LG2"/>
     <mergeCell ref="LH2:LI2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:B20 D3:D20 LH3:LH20 F3:F20 LF3:LF20 H3:H20 LD3:LD20 J3:J20 LB3:LB20 L3:L20 KZ3:KZ20 N3:N20 P3:P20 R3:R20 T3:T20 V3:V20 X3:X20 Z3:Z20 AB3:AB20 AD3:AD20 AF3:AF20 AH3:AH20 AJ3:AJ20 AL3:AL20 AN3:AN20 AP3:AP20 AR3:AR20 AT3:AT20 AV3:AV20 AX3:AX20 AZ3:AZ20 BB3:BB20 BD3:BD20 BF3:BF20 BH3:BH20 BJ3:BJ20 BL3:BL20 BN3:BN20 BP3:BP20 BR3:BR20 BT3:BT20 BV3:BV20 BX3:BX20 BZ3:BZ20 CB3:CB20 CD3:CD20 CF3:CF20 CH3:CH20 CJ3:CJ20 CL3:CL20 CN3:CN20 CP3:CP20 CR3:CR20 CT3:CT20 CV3:CV20 CX3:CX20 CZ3:CZ20 DB3:DB20 DD3:DD20 DF3:DF20 DH3:DH20 DJ3:DJ20 DL3:DL20 DN3:DN20 DP3:DP20 DR3:DR20 DT3:DT20 DV3:DV20 DX3:DX20 DZ3:DZ20 EB3:EB20 ED3:ED20 EF3:EF20 EH3:EH20 EJ3:EJ20 EL3:EL20 EN3:EN20 EP3:EP20 ER3:ER20 ET3:ET20 EV3:EV20 EX3:EX20 EZ3:EZ20 FB3:FB20 FD3:FD20 FF3:FF20 FH3:FH20 FJ3:FJ20 FL3:FL20 FN3:FN20 FP3:FP20 FR3:FR20 FT3:FT20 FV3:FV20 FX3:FX20 FZ3:FZ20 GB3:GB20 GD3:GD20 GF3:GF20 GH3:GH20 GJ3:GJ20 GL3:GL20 GN3:GN20 GP3:GP20 GR3:GR20 GT3:GT20 GV3:GV20 GX3:GX20 GZ3:GZ20 HB3:HB20 HD3:HD20 HF3:HF20 HH3:HH20 HJ3:HJ20 HL3:HL20 HN3:HN20 HP3:HP20 HR3:HR20 HT3:HT20 HV3:HV20 HX3:HX20 HZ3:HZ20 IB3:IB20 ID3:ID20 IF3:IF20 IH3:IH20 IJ3:IJ20 IL3:IL20 IN3:IN20 IP3:IP20 IR3:IR20 IT3:IT20 IV3:IV20 IX3:IX20 IZ3:IZ20 JB3:JB20 JD3:JD20 JF3:JF20 JH3:JH20 JJ3:JJ20 JL3:JL20 JN3:JN20 JP3:JP20 JR3:JR20 JT3:JT20 JV3:JV20 JX3:JX20 JZ3:JZ20 KB3:KB20 KD3:KD20 KF3:KF20 KH3:KH20 KJ3:KJ20 KL3:KL20 KN3:KN20 KP3:KP20 KR3:KR20 KT3:KT20 KV3:KV20 KX3:KX20">
+  <conditionalFormatting sqref="B3:B20 D3:D20 LH3:LH20 KW10:LG10 F3:F20 LF3:LF9 LF11:LF20 H3:H20 LD3:LD9 LD11:LD20 J3:J20 LB3:LB9 LB11:LB20 L3:L20 KZ3:KZ9 KZ11:KZ20 N3:N20 P3:P20 R3:R20 T3:T20 V3:V20 X3:X20 W10 Z3:Z20 Y10 AB3:AB20 AA10 AD3:AD20 AC10 AF3:AF20 AE10 AH3:AH20 AG10 AJ3:AJ20 AI10 AL3:AL20 AK10 AN3:AN20 AM10 AP3:AP20 AO10 AR3:AR20 AQ10 AT3:AT20 AS10 AV3:AV20 AU10 AX3:AX20 AW10 AZ3:AZ20 AY10 BB3:BB20 BA10 BD3:BD20 BC10 BF3:BF20 BE10 BH3:BH20 BG10 BJ3:BJ20 BI10 BL3:BL20 BK10 BN3:BN20 BM10 BP3:BP20 BO10 BR3:BR20 BQ10 BT3:BT20 BS10 BV3:BV20 BU10 BX3:BX20 BW10 BZ3:BZ20 BY10 CB3:CB20 CA10 CD3:CD20 CC10 CF3:CF20 CE10 CH3:CH20 CG10 CJ3:CJ20 CI10 CL3:CL20 CK10 CN3:CN20 CM10 CP3:CP20 CO10 CR3:CR20 CQ10 CT3:CT20 CS10 CV3:CV20 CU10 CX3:CX20 CW10 CZ3:CZ20 CY10 DB3:DB20 DA10 DD3:DD20 DC10 DF3:DF20 DE10 DH3:DH20 DG10 DJ3:DJ20 DI10 DL3:DL20 DK10 DN3:DN20 DM10 DP3:DP20 DO10 DR3:DR20 DQ10 DT3:DT20 DS10 DV3:DV20 DU10 DX3:DX20 DW10 DZ3:DZ20 DY10 EB3:EB20 EA10 ED3:ED20 EC10 EF3:EF20 EE10 EH3:EH20 EG10 EJ3:EJ20 EI10 EL3:EL20 EK10 EN3:EN20 EM10 EP3:EP20 EO10 ER3:ER20 EQ10 ET3:ET20 ES10 EV3:EV20 EU10 EX3:EX20 EW10 EZ3:EZ20 EY10 FB3:FB20 FA10 FD3:FD20 FC10 FF3:FF20 FE10 FH3:FH20 FG10 FJ3:FJ20 FI10 FL3:FL20 FK10 FN3:FN20 FM10 FP3:FP20 FO10 FR3:FR20 FQ10 FT3:FT20 FS10 FV3:FV20 FU10 FX3:FX20 FW10 FZ3:FZ20 FY10 GB3:GB20 GA10 GD3:GD20 GC10 GF3:GF20 GE10 GH3:GH20 GG10 GJ3:GJ20 GI10 GL3:GL20 GK10 GN3:GN20 GM10 GP3:GP20 GO10 GR3:GR20 GQ10 GT3:GT20 GS10 GV3:GV20 GU10 GX3:GX20 GW10 GZ3:GZ20 GY10 HB3:HB20 HA10 HD3:HD20 HC10 HF3:HF20 HE10 HH3:HH20 HG10 HJ3:HJ20 HI10 HL3:HL20 HK10 HN3:HN20 HM10 HP3:HP20 HO10 HR3:HR20 HQ10 HT3:HT20 HS10 HV3:HV20 HU10 HX3:HX20 HW10 HZ3:HZ20 HY10 IB3:IB20 IA10 ID3:ID20 IC10 IF3:IF20 IE10 IH3:IH20 IG10 IJ3:IJ20 II10 IL3:IL20 IK10 IN3:IN20 IM10 IP3:IP20 IO10 IR3:IR20 IQ10 IT3:IT20 IS10 IV3:IV20 IU10 IX3:IX20 IW10 IZ3:IZ20 IY10 JB3:JB20 JA10 JD3:JD20 JC10 JF3:JF20 JE10 JH3:JH20 JG10 JJ3:JJ20 JI10 JL3:JL20 JK10 JN3:JN20 JM10 JP3:JP20 JO10 JR3:JR20 JQ10 JT3:JT20 JS10 JV3:JV20 JU10 JX3:JX20 JW10 JZ3:JZ20 JY10 KB3:KB20 KA10 KD3:KD20 KC10 KF3:KF20 KE10 KH3:KH20 KG10 KJ3:KJ20 KI10 KL3:KL20 KK10 KN3:KN20 KM10 KP3:KP20 KO10 KR3:KR20 KQ10 KT3:KT20 KS10 KV3:KV20 KU10 KX3:KX9 KX11:KX20 LI10">
     <cfRule type="containsText" dxfId="0" priority="5" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",B3)))</formula>
     </cfRule>
@@ -9582,28 +9818,28 @@
       <formula>LEN(TRIM(C3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C20 E3:E20 LI3:LI20 G3:G20 LG3:LG20 I3:I20 LE3:LE20 K3:K20 LC3:LC20 M3:M20 LA3:LA20 O3:O20 Q3:Q20 S3:S20 U3:U20 W3:W20 Y3:Y20 AA3:AA20 AC3:AC20 AE3:AE20 AG3:AG20 AI3:AI20 AK3:AK20 AM3:AM20 AO3:AO20 AQ3:AQ20 AS3:AS20 AU3:AU20 AW3:AW20 AY3:AY20 BA3:BA20 BC3:BC20 BE3:BE20 BG3:BG20 BI3:BI20 BK3:BK20 BM3:BM20 BO3:BO20 BQ3:BQ20 BS3:BS20 BU3:BU20 BW3:BW20 BY3:BY20 CA3:CA20 CC3:CC20 CE3:CE20 CG3:CG20 CI3:CI20 CK3:CK20 CM3:CM20 CO3:CO20 CQ3:CQ20 CS3:CS20 CU3:CU20 CW3:CW20 CY3:CY20 DA3:DA20 DC3:DC20 DE3:DE20 DG3:DG20 DI3:DI20 DK3:DK20 DM3:DM20 DO3:DO20 DQ3:DQ20 DS3:DS20 DU3:DU20 DW3:DW20 DY3:DY20 EA3:EA20 EC3:EC20 EE3:EE20 EG3:EG20 EI3:EI20 EK3:EK20 EM3:EM20 EO3:EO20 EQ3:EQ20 ES3:ES20 EU3:EU20 EW3:EW20 EY3:EY20 FA3:FA20 FC3:FC20 FE3:FE20 FG3:FG20 FI3:FI20 FK3:FK20 FM3:FM20 FO3:FO20 FQ3:FQ20 FS3:FS20 FU3:FU20 FW3:FW20 FY3:FY20 GA3:GA20 GC3:GC20 GE3:GE20 GG3:GG20 GI3:GI20 GK3:GK20 GM3:GM20 GO3:GO20 GQ3:GQ20 GS3:GS20 GU3:GU20 GW3:GW20 GY3:GY20 HA3:HA20 HC3:HC20 HE3:HE20 HG3:HG20 HI3:HI20 HK3:HK20 HM3:HM20 HO3:HO20 HQ3:HQ20 HS3:HS20 HU3:HU20 HW3:HW20 HY3:HY20 IA3:IA20 IC3:IC20 IE3:IE20 IG3:IG20 II3:II20 IK3:IK20 IM3:IM20 IO3:IO20 IQ3:IQ20 IS3:IS20 IU3:IU20 IW3:IW20 IY3:IY20 JA3:JA20 JC3:JC20 JE3:JE20 JG3:JG20 JI3:JI20 JK3:JK20 JM3:JM20 JO3:JO20 JQ3:JQ20 JS3:JS20 JU3:JU20 JW3:JW20 JY3:JY20 KA3:KA20 KC3:KC20 KE3:KE20 KG3:KG20 KI3:KI20 KK3:KK20 KM3:KM20 KO3:KO20 KQ3:KQ20 KS3:KS20 KU3:KU20 KW3:KW20 KY3:KY20">
+  <conditionalFormatting sqref="C3:C20 E3:E20 LI3:LI20 KX10:LH10 G3:G20 LG3:LG9 LG11:LG20 I3:I20 LE3:LE9 LE11:LE20 K3:K20 LC3:LC9 LC11:LC20 M3:M20 LA3:LA9 LA11:LA20 O3:O20 Q3:Q20 S3:S20 U3:U20 W3:W20 Y3:Y20 X10 AA3:AA20 Z10 AC3:AC20 AB10 AE3:AE20 AD10 AG3:AG20 AF10 AI3:AI20 AH10 AK3:AK20 AJ10 AM3:AM20 AL10 AO3:AO20 AN10 AQ3:AQ20 AP10 AS3:AS20 AR10 AU3:AU20 AT10 AW3:AW20 AV10 AY3:AY20 AX10 BA3:BA20 AZ10 BC3:BC20 BB10 BE3:BE20 BD10 BG3:BG20 BF10 BI3:BI20 BH10 BK3:BK20 BJ10 BM3:BM20 BL10 BO3:BO20 BN10 BQ3:BQ20 BP10 BS3:BS20 BR10 BU3:BU20 BT10 BW3:BW20 BV10 BY3:BY20 BX10 CA3:CA20 BZ10 CC3:CC20 CB10 CE3:CE20 CD10 CG3:CG20 CF10 CI3:CI20 CH10 CK3:CK20 CJ10 CM3:CM20 CL10 CO3:CO20 CN10 CQ3:CQ20 CP10 CS3:CS20 CR10 CU3:CU20 CT10 CW3:CW20 CV10 CY3:CY20 CX10 DA3:DA20 CZ10 DC3:DC20 DB10 DE3:DE20 DD10 DG3:DG20 DF10 DI3:DI20 DH10 DK3:DK20 DJ10 DM3:DM20 DL10 DO3:DO20 DN10 DQ3:DQ20 DP10 DS3:DS20 DR10 DU3:DU20 DT10 DW3:DW20 DV10 DY3:DY20 DX10 EA3:EA20 DZ10 EC3:EC20 EB10 EE3:EE20 ED10 EG3:EG20 EF10 EI3:EI20 EH10 EK3:EK20 EJ10 EM3:EM20 EL10 EO3:EO20 EN10 EQ3:EQ20 EP10 ES3:ES20 ER10 EU3:EU20 ET10 EW3:EW20 EV10 EY3:EY20 EX10 FA3:FA20 EZ10 FC3:FC20 FB10 FE3:FE20 FD10 FG3:FG20 FF10 FI3:FI20 FH10 FK3:FK20 FJ10 FM3:FM20 FL10 FO3:FO20 FN10 FQ3:FQ20 FP10 FS3:FS20 FR10 FU3:FU20 FT10 FW3:FW20 FV10 FY3:FY20 FX10 GA3:GA20 FZ10 GC3:GC20 GB10 GE3:GE20 GD10 GG3:GG20 GF10 GI3:GI20 GH10 GK3:GK20 GJ10 GM3:GM20 GL10 GO3:GO20 GN10 GQ3:GQ20 GP10 GS3:GS20 GR10 GU3:GU20 GT10 GW3:GW20 GV10 GY3:GY20 GX10 HA3:HA20 GZ10 HC3:HC20 HB10 HE3:HE20 HD10 HG3:HG20 HF10 HI3:HI20 HH10 HK3:HK20 HJ10 HM3:HM20 HL10 HO3:HO20 HN10 HQ3:HQ20 HP10 HS3:HS20 HR10 HU3:HU20 HT10 HW3:HW20 HV10 HY3:HY20 HX10 IA3:IA20 HZ10 IC3:IC20 IB10 IE3:IE20 ID10 IG3:IG20 IF10 II3:II20 IH10 IK3:IK20 IJ10 IM3:IM20 IL10 IO3:IO20 IN10 IQ3:IQ20 IP10 IS3:IS20 IR10 IU3:IU20 IT10 IW3:IW20 IV10 IY3:IY20 IX10 JA3:JA20 IZ10 JC3:JC20 JB10 JE3:JE20 JD10 JG3:JG20 JF10 JI3:JI20 JH10 JK3:JK20 JJ10 JM3:JM20 JL10 JO3:JO20 JN10 JQ3:JQ20 JP10 JS3:JS20 JR10 JU3:JU20 JT10 JW3:JW20 JV10 JY3:JY20 JX10 KA3:KA20 JZ10 KC3:KC20 KB10 KE3:KE20 KD10 KG3:KG20 KF10 KI3:KI20 KH10 KK3:KK20 KJ10 KM3:KM20 KL10 KO3:KO20 KN10 KQ3:KQ20 KP10 KS3:KS20 KR10 KU3:KU20 KT10 KW3:KW20 KV10 KY3:KY9 KY11:KY20">
     <cfRule type="containsText" dxfId="2" priority="4" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21 E21 G21 I21 K21 M21 O21 Q21 S21 U21 W21 Y21 AA21 AC21 AE21 AG21 AI21 AK21 AM21 AO21 AQ21 AS21 AU21 AW21 AY21 BA21 BC21 BE21 BG21 BI21 BK21 BM21 BO21 BQ21 BS21 BU21 BW21 BY21 CA21 CC21 CE21 CG21 CI21 CK21 CM21 CO21 CQ21 CS21 CU21 CW21 CY21 DA21 DC21 DE21 DG21 DI21 DK21 DM21 DO21 DQ21 DS21 DU21 DW21 DY21 EA21 EC21 EE21 EG21 EI21 EK21 EM21 EO21 EQ21 ES21 EU21 EW21 EY21 FA21 FC21 FE21 FG21 FI21 FK21 FM21 FO21 FQ21 FS21 FU21 FW21 FY21 GA21 GC21 GE21 GG21 GI21 GK21 GM21 GO21 GQ21 GS21 GU21 GW21 GY21 HA21 HC21 HE21 HG21 HI21 HK21 HM21 HO21 HQ21 HS21 HU21 HW21 HY21 IA21 IC21 IE21 IG21 II21 IK21 IM21 IO21 IQ21 IS21 IU21 IW21 IY21 JA21 JC21 JE21 JG21 JI21 JK21 JM21 JO21 JQ21 JS21 JU21 JW21 JY21 KA21 KC21 KE21 KG21 KI21 KK21 KM21 KO21 KQ21 KS21 KU21 KW21 KY21 LA21 LC21 LE21 LG21 LI21">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C21)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="4" priority="1">
+    <cfRule type="containsBlanks" dxfId="3" priority="1">
       <formula>LEN(TRIM(C21))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3 Y7 Y8 Y9 U10 W10 Y10 AA10 AC10 AE10 AG10 AI10 AK10 AM10 AO10 AQ10 AS10 AU10 AW10 AY10 BA10 BC10 BE10 BG10 BI10 BK10 BM10 BO10 BQ10 BS10 BU10 BW10 BY10 CA10 CC10 CE10 CG10 CI10 CK10 CM10 CO10 CQ10 CS10 CU10 CW10 CY10 DA10 DC10 DE10 DG10 DI10 DK10 DM10 DO10 DQ10 DS10 DU10 DW10 DY10 EA10 EC10 EE10 EG10 EI10 EK10 EM10 EO10 EQ10 ES10 EU10 EW10 EY10 FA10 FC10 FE10 FG10 FI10 FK10 FM10 FO10 FQ10 FS10 FU10 FW10 FY10 GA10 GC10 GE10 GG10 GI10 GK10 GM10 GO10 GQ10 GS10 GU10 GW10 GY10 HA10 HC10 HE10 HG10 HI10 HK10 HM10 HO10 HQ10 HS10 HU10 HW10 HY10 IA10 IC10 IE10 IG10 II10 IK10 IM10 IO10 IQ10 IS10 IU10 IW10 IY10 JA10 JC10 JE10 JG10 JI10 JK10 JM10 JO10 JQ10 JS10 JU10 JW10 JY10 KA10 KC10 KE10 KG10 KI10 KK10 KM10 KO10 KQ10 KS10 KU10 KW10 KY10 LA10 LC10 LE10 LG10 LI10 Y11 Y15 Y19 Y20 C3:C20 E3:E20 G3:G20 I3:I20 K3:K20 M3:M20 O3:O20 Q3:Q20 S3:S20 U3:U9 U11:U20 W3:W9 W11:W20 Y4:Y6 Y12:Y14 Y16:Y18 AA3:AA9 AA11:AA20 AC3:AC9 AC11:AC20 AE3:AE9 AE11:AE20 AG3:AG9 AG11:AG20 AI3:AI9 AI11:AI20 AK3:AK9 AK11:AK20 AM3:AM9 AM11:AM20 AO3:AO9 AO11:AO20 AQ3:AQ9 AQ11:AQ20 AS3:AS9 AS11:AS20 AU3:AU9 AU11:AU20 AW3:AW9 AW11:AW20 AY3:AY9 AY11:AY20 BA3:BA9 BA11:BA20 BC3:BC9 BC11:BC20 BE3:BE9 BE11:BE20 BG3:BG9 BG11:BG20 BI3:BI9 BI11:BI20 BK3:BK9 BK11:BK20 BM3:BM9 BM11:BM20 BO3:BO9 BO11:BO20 BQ3:BQ9 BQ11:BQ20 BS3:BS9 BS11:BS20 BU3:BU9 BU11:BU20 BW3:BW9 BW11:BW20 BY3:BY9 BY11:BY20 CA3:CA9 CA11:CA20 CC3:CC9 CC11:CC20 CE3:CE9 CE11:CE20 CG3:CG9 CG11:CG20 CI3:CI9 CI11:CI20 CK3:CK9 CK11:CK20 CM3:CM9 CM11:CM20 CO3:CO9 CO11:CO20 CQ3:CQ9 CQ11:CQ20 CS3:CS9 CS11:CS20 CU3:CU9 CU11:CU20 CW3:CW9 CW11:CW20 CY3:CY9 CY11:CY20 DA3:DA9 DA11:DA20 DC3:DC9 DC11:DC20 DE3:DE9 DE11:DE20 DG3:DG9 DG11:DG20 DI3:DI9 DI11:DI20 DK3:DK9 DK11:DK20 DM3:DM9 DM11:DM20 DO3:DO9 DO11:DO20 DQ3:DQ9 DQ11:DQ20 DS3:DS9 DS11:DS20 DU3:DU9 DU11:DU20 DW3:DW9 DW11:DW20 DY3:DY9 DY11:DY20 EA3:EA9 EA11:EA20 EC3:EC9 EC11:EC20 EE3:EE9 EE11:EE20 EG3:EG9 EG11:EG20 EI3:EI9 EI11:EI20 EK3:EK9 EK11:EK20 EM3:EM9 EM11:EM20 EO3:EO9 EO11:EO20 EQ3:EQ9 EQ11:EQ20 ES3:ES9 ES11:ES20 EU3:EU9 EU11:EU20 EW3:EW9 EW11:EW20 EY3:EY9 EY11:EY20 FA3:FA9 FA11:FA20 FC3:FC9 FC11:FC20 FE3:FE9 FE11:FE20 FG3:FG9 FG11:FG20 FI3:FI9 FI11:FI20 FK3:FK9 FK11:FK20 FM3:FM9 FM11:FM20 FO3:FO9 FO11:FO20 FQ3:FQ9 FQ11:FQ20 FS3:FS9 FS11:FS20 FU3:FU9 FU11:FU20 FW3:FW9 FW11:FW20 FY3:FY9 FY11:FY20 GA3:GA9 GA11:GA20 GC3:GC9 GC11:GC20 GE3:GE9 GE11:GE20 GG3:GG9 GG11:GG20 GI3:GI9 GI11:GI20 GK3:GK9 GK11:GK20 GM3:GM9 GM11:GM20 GO3:GO9 GO11:GO20 GQ3:GQ9 GQ11:GQ20 GS3:GS9 GS11:GS20 GU3:GU9 GU11:GU20 GW3:GW9 GW11:GW20 GY3:GY9 GY11:GY20 HA3:HA9 HA11:HA20 HC3:HC9 HC11:HC20 HE3:HE9 HE11:HE20 HG3:HG9 HG11:HG20 HI3:HI9 HI11:HI20 HK3:HK9 HK11:HK20 HM3:HM9 HM11:HM20 HO3:HO9 HO11:HO20 HQ3:HQ9 HQ11:HQ20 HS3:HS9 HS11:HS20 HU3:HU9 HU11:HU20 HW3:HW9 HW11:HW20 HY3:HY9 HY11:HY20 IA3:IA9 IA11:IA20 IC3:IC9 IC11:IC20 IE3:IE9 IE11:IE20 IG3:IG9 IG11:IG20 II3:II9 II11:II20 IK3:IK9 IK11:IK20 IM3:IM9 IM11:IM20 IO3:IO9 IO11:IO20 IQ3:IQ9 IQ11:IQ20 IS3:IS9 IS11:IS20 IU3:IU9 IU11:IU20 IW3:IW9 IW11:IW20 IY3:IY9 IY11:IY20 JA3:JA9 JA11:JA20 JC3:JC9 JC11:JC20 JE3:JE9 JE11:JE20 JG3:JG9 JG11:JG20 JI3:JI9 JI11:JI20 JK3:JK9 JK11:JK20 JM3:JM9 JM11:JM20 JO3:JO9 JO11:JO20 JQ3:JQ9 JQ11:JQ20 JS3:JS9 JS11:JS20 JU3:JU9 JU11:JU20 JW3:JW9 JW11:JW20 JY3:JY9 JY11:JY20 KA3:KA9 KA11:KA20 KC3:KC9 KC11:KC20 KE3:KE9 KE11:KE20 KG3:KG9 KG11:KG20 KI3:KI9 KI11:KI20 KK3:KK9 KK11:KK20 KM3:KM9 KM11:KM20 KO3:KO9 KO11:KO20 KQ3:KQ9 KQ11:KQ20 KS3:KS9 KS11:KS20 KU3:KU9 KU11:KU20 KW3:KW9 KW11:KW20 KY3:KY9 KY11:KY20 LA3:LA9 LA11:LA20 LC3:LC9 LC11:LC20 LE3:LE9 LE11:LE20 LG3:LG9 LG11:LG20 LI3:LI9 LI11:LI20">
+      <formula1>数据!$B$1:$B$55</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10 V10 X10 Z10 AB10 AD10 AF10 AH10 AJ10 AL10 AN10 AP10 AR10 AT10 AV10 AX10 AZ10 BB10 BD10 BF10 BH10 BJ10 BL10 BN10 BP10 BR10 BT10 BV10 BX10 BZ10 CB10 CD10 CF10 CH10 CJ10 CL10 CN10 CP10 CR10 CT10 CV10 CX10 CZ10 DB10 DD10 DF10 DH10 DJ10 DL10 DN10 DP10 DR10 DT10 DV10 DX10 DZ10 EB10 ED10 EF10 EH10 EJ10 EL10 EN10 EP10 ER10 ET10 EV10 EX10 EZ10 FB10 FD10 FF10 FH10 FJ10 FL10 FN10 FP10 FR10 FT10 FV10 FX10 FZ10 GB10 GD10 GF10 GH10 GJ10 GL10 GN10 GP10 GR10 GT10 GV10 GX10 GZ10 HB10 HD10 HF10 HH10 HJ10 HL10 HN10 HP10 HR10 HT10 HV10 HX10 HZ10 IB10 ID10 IF10 IH10 IJ10 IL10 IN10 IP10 IR10 IT10 IV10 IX10 IZ10 JB10 JD10 JF10 JH10 JJ10 JL10 JN10 JP10 JR10 JT10 JV10 JX10 JZ10 KB10 KD10 KF10 KH10 KJ10 KL10 KN10 KP10 KR10 KT10 KV10 KX10 KZ10 LB10 LD10 LF10 LH10 B3:B20 D3:D20 F3:F20 H3:H20 J3:J20 L3:L20 N3:N20 P3:P20 R3:R20 T3:T9 T11:T20 V3:V9 V11:V20 X3:X9 X11:X20 Z3:Z9 Z11:Z20 AB3:AB9 AB11:AB20 AD3:AD9 AD11:AD20 AF3:AF9 AF11:AF20 AH3:AH9 AH11:AH20 AJ3:AJ9 AJ11:AJ20 AL3:AL9 AL11:AL20 AN3:AN9 AN11:AN20 AP3:AP9 AP11:AP20 AR3:AR9 AR11:AR20 AT3:AT9 AT11:AT20 AV3:AV9 AV11:AV20 AX3:AX9 AX11:AX20 AZ3:AZ9 AZ11:AZ20 BB3:BB9 BB11:BB20 BD3:BD9 BD11:BD20 BF3:BF9 BF11:BF20 BH3:BH9 BH11:BH20 BJ3:BJ9 BJ11:BJ20 BL3:BL9 BL11:BL20 BN3:BN9 BN11:BN20 BP3:BP9 BP11:BP20 BR3:BR9 BR11:BR20 BT3:BT9 BT11:BT20 BV3:BV9 BV11:BV20 BX3:BX9 BX11:BX20 BZ3:BZ9 BZ11:BZ20 CB3:CB9 CB11:CB20 CD3:CD9 CD11:CD20 CF3:CF9 CF11:CF20 CH3:CH9 CH11:CH20 CJ3:CJ9 CJ11:CJ20 CL3:CL9 CL11:CL20 CN3:CN9 CN11:CN20 CP3:CP9 CP11:CP20 CR3:CR9 CR11:CR20 CT3:CT9 CT11:CT20 CV3:CV9 CV11:CV20 CX3:CX9 CX11:CX20 CZ3:CZ9 CZ11:CZ20 DB3:DB9 DB11:DB20 DD3:DD9 DD11:DD20 DF3:DF9 DF11:DF20 DH3:DH9 DH11:DH20 DJ3:DJ9 DJ11:DJ20 DL3:DL9 DL11:DL20 DN3:DN9 DN11:DN20 DP3:DP9 DP11:DP20 DR3:DR9 DR11:DR20 DT3:DT9 DT11:DT20 DV3:DV9 DV11:DV20 DX3:DX9 DX11:DX20 DZ3:DZ9 DZ11:DZ20 EB3:EB9 EB11:EB20 ED3:ED9 ED11:ED20 EF3:EF9 EF11:EF20 EH3:EH9 EH11:EH20 EJ3:EJ9 EJ11:EJ20 EL3:EL9 EL11:EL20 EN3:EN9 EN11:EN20 EP3:EP9 EP11:EP20 ER3:ER9 ER11:ER20 ET3:ET9 ET11:ET20 EV3:EV9 EV11:EV20 EX3:EX9 EX11:EX20 EZ3:EZ9 EZ11:EZ20 FB3:FB9 FB11:FB20 FD3:FD9 FD11:FD20 FF3:FF9 FF11:FF20 FH3:FH9 FH11:FH20 FJ3:FJ9 FJ11:FJ20 FL3:FL9 FL11:FL20 FN3:FN9 FN11:FN20 FP3:FP9 FP11:FP20 FR3:FR9 FR11:FR20 FT3:FT9 FT11:FT20 FV3:FV9 FV11:FV20 FX3:FX9 FX11:FX20 FZ3:FZ9 FZ11:FZ20 GB3:GB9 GB11:GB20 GD3:GD9 GD11:GD20 GF3:GF9 GF11:GF20 GH3:GH9 GH11:GH20 GJ3:GJ9 GJ11:GJ20 GL3:GL9 GL11:GL20 GN3:GN9 GN11:GN20 GP3:GP9 GP11:GP20 GR3:GR9 GR11:GR20 GT3:GT9 GT11:GT20 GV3:GV9 GV11:GV20 GX3:GX9 GX11:GX20 GZ3:GZ9 GZ11:GZ20 HB3:HB9 HB11:HB20 HD3:HD9 HD11:HD20 HF3:HF9 HF11:HF20 HH3:HH9 HH11:HH20 HJ3:HJ9 HJ11:HJ20 HL3:HL9 HL11:HL20 HN3:HN9 HN11:HN20 HP3:HP9 HP11:HP20 HR3:HR9 HR11:HR20 HT3:HT9 HT11:HT20 HV3:HV9 HV11:HV20 HX3:HX9 HX11:HX20 HZ3:HZ9 HZ11:HZ20 IB3:IB9 IB11:IB20 ID3:ID9 ID11:ID20 IF3:IF9 IF11:IF20 IH3:IH9 IH11:IH20 IJ3:IJ9 IJ11:IJ20 IL3:IL9 IL11:IL20 IN3:IN9 IN11:IN20 IP3:IP9 IP11:IP20 IR3:IR9 IR11:IR20 IT3:IT9 IT11:IT20 IV3:IV9 IV11:IV20 IX3:IX9 IX11:IX20 IZ3:IZ9 IZ11:IZ20 JB3:JB9 JB11:JB20 JD3:JD9 JD11:JD20 JF3:JF9 JF11:JF20 JH3:JH9 JH11:JH20 JJ3:JJ9 JJ11:JJ20 JL3:JL9 JL11:JL20 JN3:JN9 JN11:JN20 JP3:JP9 JP11:JP20 JR3:JR9 JR11:JR20 JT3:JT9 JT11:JT20 JV3:JV9 JV11:JV20 JX3:JX9 JX11:JX20 JZ3:JZ9 JZ11:JZ20 KB3:KB9 KB11:KB20 KD3:KD9 KD11:KD20 KF3:KF9 KF11:KF20 KH3:KH9 KH11:KH20 KJ3:KJ9 KJ11:KJ20 KL3:KL9 KL11:KL20 KN3:KN9 KN11:KN20 KP3:KP9 KP11:KP20 KR3:KR9 KR11:KR20 KT3:KT9 KT11:KT20 KV3:KV9 KV11:KV20 KX3:KX9 KX11:KX20 KZ3:KZ9 KZ11:KZ20 LB3:LB9 LB11:LB20 LD3:LD9 LD11:LD20 LF3:LF9 LF11:LF20 LH3:LH9 LH11:LH20">
+      <formula1>数据!$A$1:$A$88</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C21 E21 G21 I21 K21 M21 O21 Q21 S21 U21 W21 Y21 AA21 AC21 AE21 AG21 AI21 AK21 AM21 AO21 AQ21 AS21 AU21 AW21 AY21 BA21 BC21 BE21 BG21 BI21 BK21 BM21 BO21 BQ21 BS21 BU21 BW21 BY21 CA21 CC21 CE21 CG21 CI21 CK21 CM21 CO21 CQ21 CS21 CU21 CW21 CY21 DA21 DC21 DE21 DG21 DI21 DK21 DM21 DO21 DQ21 DS21 DU21 DW21 DY21 EA21 EC21 EE21 EG21 EI21 EK21 EM21 EO21 EQ21 ES21 EU21 EW21 EY21 FA21 FC21 FE21 FG21 FI21 FK21 FM21 FO21 FQ21 FS21 FU21 FW21 FY21 GA21 GC21 GE21 GG21 GI21 GK21 GM21 GO21 GQ21 GS21 GU21 GW21 GY21 HA21 HC21 HE21 HG21 HI21 HK21 HM21 HO21 HQ21 HS21 HU21 HW21 HY21 IA21 IC21 IE21 IG21 II21 IK21 IM21 IO21 IQ21 IS21 IU21 IW21 IY21 JA21 JC21 JE21 JG21 JI21 JK21 JM21 JO21 JQ21 JS21 JU21 JW21 JY21 KA21 KC21 KE21 KG21 KI21 KK21 KM21 KO21 KQ21 KS21 KU21 KW21 KY21 LA21 LC21 LE21 LG21 LI21">
       <formula1>数据!$C$1:$C$25</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B20 D3:D20 F3:F20 H3:H20 J3:J20 L3:L20 N3:N20 P3:P20 R3:R20 T3:T20 V3:V20 X3:X20 Z3:Z20 AB3:AB20 AD3:AD20 AF3:AF20 AH3:AH20 AJ3:AJ20 AL3:AL20 AN3:AN20 AP3:AP20 AR3:AR20 AT3:AT20 AV3:AV20 AX3:AX20 AZ3:AZ20 BB3:BB20 BD3:BD20 BF3:BF20 BH3:BH20 BJ3:BJ20 BL3:BL20 BN3:BN20 BP3:BP20 BR3:BR20 BT3:BT20 BV3:BV20 BX3:BX20 BZ3:BZ20 CB3:CB20 CD3:CD20 CF3:CF20 CH3:CH20 CJ3:CJ20 CL3:CL20 CN3:CN20 CP3:CP20 CR3:CR20 CT3:CT20 CV3:CV20 CX3:CX20 CZ3:CZ20 DB3:DB20 DD3:DD20 DF3:DF20 DH3:DH20 DJ3:DJ20 DL3:DL20 DN3:DN20 DP3:DP20 DR3:DR20 DT3:DT20 DV3:DV20 DX3:DX20 DZ3:DZ20 EB3:EB20 ED3:ED20 EF3:EF20 EH3:EH20 EJ3:EJ20 EL3:EL20 EN3:EN20 EP3:EP20 ER3:ER20 ET3:ET20 EV3:EV20 EX3:EX20 EZ3:EZ20 FB3:FB20 FD3:FD20 FF3:FF20 FH3:FH20 FJ3:FJ20 FL3:FL20 FN3:FN20 FP3:FP20 FR3:FR20 FT3:FT20 FV3:FV20 FX3:FX20 FZ3:FZ20 GB3:GB20 GD3:GD20 GF3:GF20 GH3:GH20 GJ3:GJ20 GL3:GL20 GN3:GN20 GP3:GP20 GR3:GR20 GT3:GT20 GV3:GV20 GX3:GX20 GZ3:GZ20 HB3:HB20 HD3:HD20 HF3:HF20 HH3:HH20 HJ3:HJ20 HL3:HL20 HN3:HN20 HP3:HP20 HR3:HR20 HT3:HT20 HV3:HV20 HX3:HX20 HZ3:HZ20 IB3:IB20 ID3:ID20 IF3:IF20 IH3:IH20 IJ3:IJ20 IL3:IL20 IN3:IN20 IP3:IP20 IR3:IR20 IT3:IT20 IV3:IV20 IX3:IX20 IZ3:IZ20 JB3:JB20 JD3:JD20 JF3:JF20 JH3:JH20 JJ3:JJ20 JL3:JL20 JN3:JN20 JP3:JP20 JR3:JR20 JT3:JT20 JV3:JV20 JX3:JX20 JZ3:JZ20 KB3:KB20 KD3:KD20 KF3:KF20 KH3:KH20 KJ3:KJ20 KL3:KL20 KN3:KN20 KP3:KP20 KR3:KR20 KT3:KT20 KV3:KV20 KX3:KX20 KZ3:KZ20 LB3:LB20 LD3:LD20 LF3:LF20 LH3:LH20">
-      <formula1>数据!$A$1:$A$31</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C20 E3:E20 G3:G20 I3:I20 K3:K20 M3:M20 O3:O20 Q3:Q20 S3:S20 U3:U20 W3:W20 Y3:Y20 AA3:AA20 AC3:AC20 AE3:AE20 AG3:AG20 AI3:AI20 AK3:AK20 AM3:AM20 AO3:AO20 AQ3:AQ20 AS3:AS20 AU3:AU20 AW3:AW20 AY3:AY20 BA3:BA20 BC3:BC20 BE3:BE20 BG3:BG20 BI3:BI20 BK3:BK20 BM3:BM20 BO3:BO20 BQ3:BQ20 BS3:BS20 BU3:BU20 BW3:BW20 BY3:BY20 CA3:CA20 CC3:CC20 CE3:CE20 CG3:CG20 CI3:CI20 CK3:CK20 CM3:CM20 CO3:CO20 CQ3:CQ20 CS3:CS20 CU3:CU20 CW3:CW20 CY3:CY20 DA3:DA20 DC3:DC20 DE3:DE20 DG3:DG20 DI3:DI20 DK3:DK20 DM3:DM20 DO3:DO20 DQ3:DQ20 DS3:DS20 DU3:DU20 DW3:DW20 DY3:DY20 EA3:EA20 EC3:EC20 EE3:EE20 EG3:EG20 EI3:EI20 EK3:EK20 EM3:EM20 EO3:EO20 EQ3:EQ20 ES3:ES20 EU3:EU20 EW3:EW20 EY3:EY20 FA3:FA20 FC3:FC20 FE3:FE20 FG3:FG20 FI3:FI20 FK3:FK20 FM3:FM20 FO3:FO20 FQ3:FQ20 FS3:FS20 FU3:FU20 FW3:FW20 FY3:FY20 GA3:GA20 GC3:GC20 GE3:GE20 GG3:GG20 GI3:GI20 GK3:GK20 GM3:GM20 GO3:GO20 GQ3:GQ20 GS3:GS20 GU3:GU20 GW3:GW20 GY3:GY20 HA3:HA20 HC3:HC20 HE3:HE20 HG3:HG20 HI3:HI20 HK3:HK20 HM3:HM20 HO3:HO20 HQ3:HQ20 HS3:HS20 HU3:HU20 HW3:HW20 HY3:HY20 IA3:IA20 IC3:IC20 IE3:IE20 IG3:IG20 II3:II20 IK3:IK20 IM3:IM20 IO3:IO20 IQ3:IQ20 IS3:IS20 IU3:IU20 IW3:IW20 IY3:IY20 JA3:JA20 JC3:JC20 JE3:JE20 JG3:JG20 JI3:JI20 JK3:JK20 JM3:JM20 JO3:JO20 JQ3:JQ20 JS3:JS20 JU3:JU20 JW3:JW20 JY3:JY20 KA3:KA20 KC3:KC20 KE3:KE20 KG3:KG20 KI3:KI20 KK3:KK20 KM3:KM20 KO3:KO20 KQ3:KQ20 KS3:KS20 KU3:KU20 KW3:KW20 KY3:KY20 LA3:LA20 LC3:LC20 LE3:LE20 LG3:LG20 LI3:LI20">
-      <formula1>数据!$B$1:$B$55</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9614,7 +9850,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12.2727272727273" customWidth="1"/>
@@ -9677,7 +9913,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>1.25</v>
@@ -9721,7 +9957,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>2.25</v>
@@ -9754,7 +9990,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -9765,7 +10001,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>3.25</v>
@@ -9776,7 +10012,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>3.5</v>
@@ -9787,7 +10023,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>3.75</v>
@@ -9798,7 +10034,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -9809,7 +10045,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B18">
         <v>4.25</v>
@@ -9820,7 +10056,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>4.5</v>
@@ -9831,7 +10067,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>4.75</v>
@@ -9842,7 +10078,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -9853,7 +10089,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B22">
         <v>5.25</v>
@@ -9864,7 +10100,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -9875,7 +10111,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B24">
         <v>5.75</v>
@@ -9886,7 +10122,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -9897,7 +10133,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="4" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B26">
         <v>6.25</v>
@@ -9905,7 +10141,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>6.5</v>
@@ -9913,7 +10149,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28">
         <v>6.75</v>
@@ -9921,147 +10157,396 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29">
         <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>15</v>
+      <c r="A30" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="B30">
         <v>7.25</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>34</v>
+      <c r="A31" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="B31">
         <v>7.5</v>
       </c>
     </row>
-    <row r="32" spans="2:2">
+    <row r="32" spans="1:2">
+      <c r="A32" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="B32">
         <v>7.75</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="1:2">
+      <c r="A33" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="B33">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="1:2">
+      <c r="A34" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="B34">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="1:2">
+      <c r="A35" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="B35">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="2:2">
+    <row r="36" spans="1:2">
+      <c r="A36" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="B36">
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="1:2">
+      <c r="A37" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="B37">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="1:2">
+      <c r="A38" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="B38">
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="2:2">
+    <row r="39" spans="1:2">
+      <c r="A39" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="B39">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="2:2">
+    <row r="40" spans="1:2">
+      <c r="A40" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="B40">
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="2:2">
+    <row r="41" spans="1:2">
+      <c r="A41" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="B41">
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="1:2">
+      <c r="A42" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="B42">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="2:2">
+    <row r="43" spans="1:2">
+      <c r="A43" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="B43">
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="2:2">
+    <row r="44" spans="1:2">
+      <c r="A44" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="B44">
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="1:2">
+      <c r="A45" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="B45">
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="2:2">
+    <row r="46" spans="1:2">
+      <c r="A46" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="B46">
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="2:2">
+    <row r="47" spans="1:2">
+      <c r="A47" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="B47">
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="1:2">
+      <c r="A48" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="B48">
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="2:2">
+    <row r="49" spans="1:2">
+      <c r="A49" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="B49">
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="2:2">
+    <row r="50" spans="1:2">
+      <c r="A50" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="B50">
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="2:2">
+    <row r="51" spans="1:2">
+      <c r="A51" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="B51">
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="2:2">
+    <row r="52" spans="1:2">
+      <c r="A52" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="B52">
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="2:2">
+    <row r="53" spans="1:2">
+      <c r="A53" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="B53">
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="2:2">
+    <row r="54" spans="1:2">
+      <c r="A54" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="B54">
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="2:2">
+    <row r="55" spans="1:2">
+      <c r="A55" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="B55">
         <v>30</v>
       </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="4"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="4"/>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="4"/>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10081,22 +10566,22 @@
     <row r="1" ht="15" spans="1:7">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:7">
@@ -10156,7 +10641,7 @@
     </row>
     <row r="7" ht="15" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="1"/>
@@ -10200,7 +10685,7 @@
     </row>
     <row r="11" ht="15" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -10234,14 +10719,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B12">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10252,6 +10729,14 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
